--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Chennai_to_Pondicherry/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Chennai_to_Pondicherry/Average/Master_Results.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Phase_Difference_Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Descriptive_Statistics" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Route_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Plot_Audit" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,296 +430,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>pair_number</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pair_class</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>operation_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>workbook_path</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ev_tat_min</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ice_tat_min</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ev_distance_km</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ice_distance_km</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ev_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ice_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tat_min_diff</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>distance_km_diff</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>moving_speed_kmh_diff</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>stationary_time_min_diff</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_refueling_time_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_refueling_time_min</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>charging_refueling_time_diff_min</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_refueling_distance_km</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_refueling_distance_km</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>charging_refueling_distance_diff_km</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ev_stop_time_min</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ice_stop_time_min</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>stop_time_diff_min</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ev_stop_distance_km</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ice_stop_distance_km</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stop_distance_diff_km</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ev_idle_time_min</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ice_idle_time_min</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>idle_time_diff_min</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ev_idle_distance_km</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ice_idle_distance_km</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>idle_distance_diff_km</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ev_inch_time_min</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ice_inch_time_min</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>inch_time_diff_min</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ev_inch_distance_km</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>ice_inch_distance_km</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>inch_distance_diff_km</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>ev_acc_time_min</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ice_acc_time_min</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>acc_time_diff_min</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>ev_acc_distance_km</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ice_acc_distance_km</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>acc_distance_diff_km</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ev_dec_time_min</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>ice_dec_time_min</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dec_time_diff_min</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>ev_dec_distance_km</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>ice_dec_distance_km</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dec_distance_diff_km</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ev_cruise_time_min</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>ice_cruise_time_min</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>cruise_time_diff_min</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>ev_cruise_distance_km</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ice_cruise_distance_km</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>cruise_distance_diff_km</t>
         </is>
@@ -715,11 +728,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -738,7 +751,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_001_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -754,10 +767,10 @@
         <v>148.1254196841063</v>
       </c>
       <c r="K2" t="n">
-        <v>41.58535677727425</v>
+        <v>42.80810564129094</v>
       </c>
       <c r="L2" t="n">
-        <v>43.13601932523515</v>
+        <v>44.7845362014835</v>
       </c>
       <c r="M2" t="n">
         <v>-33.90636666666671</v>
@@ -766,64 +779,64 @@
         <v>0.07334933967118218</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.550662547960897</v>
+        <v>-1.976430560192554</v>
       </c>
       <c r="P2" t="n">
-        <v>13.56666666666666</v>
+        <v>-45.40000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>25.88333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.31666666666666</v>
+        <v>-43.60000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>0.3556868609874803</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.2073716941169366</v>
+        <v>-0.4841912826215016</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>8.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.25</v>
+        <v>-1.799999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-1.222149598452762</v>
       </c>
       <c r="AI2" t="n">
         <v>8.016666666666667</v>
@@ -844,22 +857,22 @@
         <v>0.05066734487869418</v>
       </c>
       <c r="AO2" t="n">
-        <v>56.05</v>
+        <v>55.88333333333333</v>
       </c>
       <c r="AP2" t="n">
         <v>25.13333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>30.91666666666667</v>
+        <v>30.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>44.91739841291827</v>
+        <v>44.7773945763174</v>
       </c>
       <c r="AS2" t="n">
         <v>16.04368253659841</v>
       </c>
       <c r="AT2" t="n">
-        <v>28.87371587631986</v>
+        <v>28.73371203971899</v>
       </c>
       <c r="AU2" t="n">
         <v>40.11666666666667</v>
@@ -880,32 +893,32 @@
         <v>14.25117348279514</v>
       </c>
       <c r="BA2" t="n">
-        <v>109.1269666666667</v>
+        <v>102.3936333333333</v>
       </c>
       <c r="BB2" t="n">
-        <v>154.5833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC2" t="n">
-        <v>-45.45636666666658</v>
+        <v>-42.2397</v>
       </c>
       <c r="BD2" t="n">
-        <v>71.26833841096357</v>
+        <v>70.83249221561701</v>
       </c>
       <c r="BE2" t="n">
-        <v>113.8863544926646</v>
+        <v>112.0883548622644</v>
       </c>
       <c r="BF2" t="n">
-        <v>-42.61801608170103</v>
+        <v>-41.25586264664739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,7 +937,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_002_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -940,7 +953,7 @@
         <v>141.6711046862772</v>
       </c>
       <c r="K3" t="n">
-        <v>46.13817614056148</v>
+        <v>47.25384199133067</v>
       </c>
       <c r="L3" t="n">
         <v>44.82161408578494</v>
@@ -952,64 +965,64 @@
         <v>-0.04910155251721449</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31656205477654</v>
+        <v>2.43222790554573</v>
       </c>
       <c r="P3" t="n">
-        <v>22.34999999999999</v>
+        <v>-0.9833333333333378</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>25.88333333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>3.533333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>22.34999999999999</v>
+        <v>-5.916666666666671</v>
       </c>
       <c r="Z3" t="n">
         <v>0.3556868609874803</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2489340406807565</v>
+        <v>0.1341259604332779</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.4693593484285414</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.4693593484285414</v>
       </c>
       <c r="AI3" t="n">
         <v>5.933333333333334</v>
@@ -1030,22 +1043,22 @@
         <v>0.2400310166415557</v>
       </c>
       <c r="AO3" t="n">
-        <v>52.5</v>
+        <v>52.33333333333334</v>
       </c>
       <c r="AP3" t="n">
         <v>30.46666666666667</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22.03333333333333</v>
+        <v>21.86666666666667</v>
       </c>
       <c r="AR3" t="n">
-        <v>43.39133179794914</v>
+        <v>43.25132796134825</v>
       </c>
       <c r="AS3" t="n">
         <v>21.52228685090974</v>
       </c>
       <c r="AT3" t="n">
-        <v>21.8690449470394</v>
+        <v>21.72904111043851</v>
       </c>
       <c r="AU3" t="n">
         <v>37.57496666666667</v>
@@ -1066,32 +1079,32 @@
         <v>13.2094183814526</v>
       </c>
       <c r="BA3" t="n">
-        <v>87.70028333333333</v>
+        <v>82.93361666666667</v>
       </c>
       <c r="BB3" t="n">
         <v>134.3833333333333</v>
       </c>
       <c r="BC3" t="n">
-        <v>-46.68304999999997</v>
+        <v>-51.44971666666663</v>
       </c>
       <c r="BD3" t="n">
-        <v>67.23643719629696</v>
+        <v>66.9070816844693</v>
       </c>
       <c r="BE3" t="n">
         <v>102.738159054381</v>
       </c>
       <c r="BF3" t="n">
-        <v>-35.50172185808404</v>
+        <v>-35.8310773699117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1110,7 +1123,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_003_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1126,10 +1139,10 @@
         <v>148.150219573912</v>
       </c>
       <c r="K4" t="n">
-        <v>46.35627936949886</v>
+        <v>49.30661820086556</v>
       </c>
       <c r="L4" t="n">
-        <v>43.14328255361949</v>
+        <v>44.79217019920052</v>
       </c>
       <c r="M4" t="n">
         <v>-52.83291666666673</v>
@@ -1138,64 +1151,64 @@
         <v>0.05819237141599842</v>
       </c>
       <c r="O4" t="n">
-        <v>3.212996815879364</v>
+        <v>4.514448001665038</v>
       </c>
       <c r="P4" t="n">
-        <v>-6.300000000000003</v>
+        <v>-34.95848333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-32.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1574257220881389</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>7.266666666666667</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X4" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>-6.300000000000003</v>
+        <v>-39.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2993866064237053</v>
+        <v>-0.4568123285118442</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>14.29151666666667</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>4.341516666666671</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.33611605697715</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>0.5381164265769423</v>
       </c>
       <c r="AI4" t="n">
         <v>2.1</v>
@@ -1234,50 +1247,50 @@
         <v>22.59238767912366</v>
       </c>
       <c r="AU4" t="n">
-        <v>34.2</v>
+        <v>33.45</v>
       </c>
       <c r="AV4" t="n">
         <v>23.43333333333333</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.76666666666667</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="AX4" t="n">
-        <v>26.86273516629103</v>
+        <v>26.28668300273065</v>
       </c>
       <c r="AY4" t="n">
         <v>16.77959665852362</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.08313850776741</v>
+        <v>9.507086344207032</v>
       </c>
       <c r="BA4" t="n">
-        <v>106.9415166666667</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>154.5833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC4" t="n">
-        <v>-47.64181666666659</v>
+        <v>-51.23333333333329</v>
       </c>
       <c r="BD4" t="n">
-        <v>82.12192653794388</v>
+        <v>80.36186264452711</v>
       </c>
       <c r="BE4" t="n">
-        <v>113.9111543824703</v>
+        <v>112.1131547520701</v>
       </c>
       <c r="BF4" t="n">
-        <v>-31.78922784452642</v>
+        <v>-31.75129210754299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1296,7 +1309,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_004_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1312,10 +1325,10 @@
         <v>146.1941703909393</v>
       </c>
       <c r="K5" t="n">
-        <v>43.31882927503337</v>
+        <v>44.76153869689547</v>
       </c>
       <c r="L5" t="n">
-        <v>44.09960930384722</v>
+        <v>44.84902776787012</v>
       </c>
       <c r="M5" t="n">
         <v>-36.32509999999999</v>
@@ -1324,64 +1337,64 @@
         <v>-0.08380816122308943</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7807800288138438</v>
+        <v>-0.08748907097464809</v>
       </c>
       <c r="P5" t="n">
-        <v>19.90823333333333</v>
+        <v>-36.49176666666666</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>29.40441666666667</v>
       </c>
       <c r="X5" t="n">
-        <v>11.26666666666667</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.13775</v>
+        <v>-41.67891666666666</v>
       </c>
       <c r="Z5" t="n">
         <v>0.4715380269015641</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.323446270295476</v>
+        <v>0.56746055645719</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1480917566060881</v>
+        <v>-0.09592252955562586</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.770483333333333</v>
+        <v>9.237150000000002</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.770483333333333</v>
+        <v>5.187150000000002</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.003326781778833682</v>
+        <v>0.7233426716155921</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.003326781778833682</v>
+        <v>0.1707796029244358</v>
       </c>
       <c r="AI5" t="n">
         <v>8.016666666666667</v>
@@ -1402,68 +1415,68 @@
         <v>-0.3789216114271208</v>
       </c>
       <c r="AO5" t="n">
-        <v>55.21666666666667</v>
+        <v>55.05</v>
       </c>
       <c r="AP5" t="n">
         <v>38.68333333333333</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.53333333333334</v>
+        <v>16.36666666666667</v>
       </c>
       <c r="AR5" t="n">
-        <v>44.51243008835447</v>
+        <v>44.37242625175359</v>
       </c>
       <c r="AS5" t="n">
         <v>27.60990969505806</v>
       </c>
       <c r="AT5" t="n">
-        <v>16.90252039329641</v>
+        <v>16.76251655669553</v>
       </c>
       <c r="AU5" t="n">
         <v>38.85</v>
       </c>
       <c r="AV5" t="n">
-        <v>27.13333333333333</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.71666666666667</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="AX5" t="n">
         <v>30.69503766819436</v>
       </c>
       <c r="AY5" t="n">
-        <v>19.99447365781878</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.70056401037558</v>
+        <v>10.80210939628688</v>
       </c>
       <c r="BA5" t="n">
-        <v>99.63333333333334</v>
+        <v>92.33333333333333</v>
       </c>
       <c r="BB5" t="n">
-        <v>120.7166666666667</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BC5" t="n">
-        <v>-21.08333333333336</v>
+        <v>-24.64999999999998</v>
       </c>
       <c r="BD5" t="n">
-        <v>69.80145446689757</v>
+        <v>69.22144241366169</v>
       </c>
       <c r="BE5" t="n">
-        <v>97.0168296725888</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BF5" t="n">
-        <v>-27.21537520569123</v>
+        <v>-27.34436957614724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1482,7 +1495,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1498,10 +1511,10 @@
         <v>147.7347082243865</v>
       </c>
       <c r="K6" t="n">
-        <v>47.1164527446597</v>
+        <v>48.10943109063845</v>
       </c>
       <c r="L6" t="n">
-        <v>43.36902945799262</v>
+        <v>45.04354059322232</v>
       </c>
       <c r="M6" t="n">
         <v>-72.92863333333338</v>
@@ -1510,64 +1523,64 @@
         <v>0.07167266537967976</v>
       </c>
       <c r="O6" t="n">
-        <v>3.747423286667086</v>
+        <v>3.065890497416135</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.53333333333334</v>
+        <v>-62.65000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>12.03333333333333</v>
       </c>
       <c r="X6" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.53333333333334</v>
+        <v>-57.45</v>
       </c>
       <c r="Z6" t="n">
         <v>0.3736603870816042</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1893981680228127</v>
+        <v>-0.4662177565273777</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-5.199999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.7015215125621636</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-1.096478117838044</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1624,36 +1637,36 @@
         <v>10.83106184492432</v>
       </c>
       <c r="BA6" t="n">
-        <v>105.2968</v>
+        <v>100.5468</v>
       </c>
       <c r="BB6" t="n">
-        <v>153.4</v>
+        <v>143.45</v>
       </c>
       <c r="BC6" t="n">
-        <v>-48.1032</v>
+        <v>-42.90319999999998</v>
       </c>
       <c r="BD6" t="n">
-        <v>82.21470927818682</v>
+        <v>81.51318776562465</v>
       </c>
       <c r="BE6" t="n">
-        <v>113.6030563965588</v>
+        <v>111.8050567661586</v>
       </c>
       <c r="BF6" t="n">
-        <v>-31.38834711837198</v>
+        <v>-30.29186900053395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1668,178 +1681,178 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_011_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_25-09-2026\PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>205.6434166666667</v>
+        <v>247.26765</v>
       </c>
       <c r="H7" t="n">
-        <v>221.15</v>
+        <v>274.35</v>
       </c>
       <c r="I7" t="n">
-        <v>141.5990549680233</v>
+        <v>148.4081122812309</v>
       </c>
       <c r="J7" t="n">
-        <v>141.6663057069586</v>
+        <v>148.1693420519742</v>
       </c>
       <c r="K7" t="n">
-        <v>48.28995397818726</v>
+        <v>47.63775321159345</v>
       </c>
       <c r="L7" t="n">
-        <v>44.82009341634151</v>
+        <v>44.79805655414056</v>
       </c>
       <c r="M7" t="n">
-        <v>-15.50658333333331</v>
+        <v>-27.08235000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0672507389353143</v>
+        <v>0.2387702292566871</v>
       </c>
       <c r="O7" t="n">
-        <v>3.469860561845756</v>
+        <v>2.83969665745289</v>
       </c>
       <c r="P7" t="n">
-        <v>3.733333333333333</v>
+        <v>-17.70095000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.349999999999998</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0045857861689476</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>7.266666666666667</v>
+        <v>35.56666666666667</v>
       </c>
       <c r="X7" t="n">
-        <v>3.533333333333333</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.733333333333333</v>
+        <v>-33.91666666666666</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.5933262321891101</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1569191283739878</v>
+        <v>-0.2465519114198719</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>26.16571666666666</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>16.21571666666666</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.5067319571443681</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-1.29126767325584</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.5</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.3333333333333328</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2046142102738726</v>
+        <v>0.1799078409944621</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0881394731161023</v>
+        <v>-0.396000011716256</v>
       </c>
       <c r="AO7" t="n">
-        <v>43.83333333333334</v>
+        <v>63.03526666666667</v>
       </c>
       <c r="AP7" t="n">
-        <v>30.46666666666667</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13.36666666666667</v>
+        <v>37.90193333333335</v>
       </c>
       <c r="AR7" t="n">
-        <v>36.80847059423598</v>
+        <v>45.7896379485424</v>
       </c>
       <c r="AS7" t="n">
-        <v>21.52025885865341</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="AT7" t="n">
-        <v>15.28821173558257</v>
+        <v>29.74595541194399</v>
       </c>
       <c r="AU7" t="n">
-        <v>30.75</v>
+        <v>45.45</v>
       </c>
       <c r="AV7" t="n">
-        <v>23</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.75</v>
+        <v>22.01666666666667</v>
       </c>
       <c r="AX7" t="n">
-        <v>25.36797775428393</v>
+        <v>33.36307095293761</v>
       </c>
       <c r="AY7" t="n">
-        <v>17.06985215621225</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.298125598071682</v>
+        <v>16.58347429441399</v>
       </c>
       <c r="BA7" t="n">
-        <v>98.77674999999999</v>
+        <v>75</v>
       </c>
       <c r="BB7" t="n">
-        <v>134.3833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC7" t="n">
-        <v>-35.6065833333333</v>
+        <v>-69.6333333333333</v>
       </c>
       <c r="BD7" t="n">
-        <v>78.83492659413233</v>
+        <v>67.97543734942298</v>
       </c>
       <c r="BE7" t="n">
-        <v>102.738159054381</v>
+        <v>112.1322772301322</v>
       </c>
       <c r="BF7" t="n">
-        <v>-23.90323246024867</v>
+        <v>-44.15683988070923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1854,174 +1867,174 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_012_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>219.9365833333333</v>
+        <v>205.6434166666667</v>
       </c>
       <c r="H8" t="n">
-        <v>269.2166666666666</v>
+        <v>221.15</v>
       </c>
       <c r="I8" t="n">
-        <v>146.1177802267258</v>
+        <v>141.5990549680233</v>
       </c>
       <c r="J8" t="n">
-        <v>146.2265476173816</v>
+        <v>141.6663057069586</v>
       </c>
       <c r="K8" t="n">
-        <v>46.08133386225383</v>
+        <v>51.08928882117495</v>
       </c>
       <c r="L8" t="n">
-        <v>44.10804715430679</v>
+        <v>44.82009341634151</v>
       </c>
       <c r="M8" t="n">
-        <v>-49.28008333333329</v>
+        <v>-15.50658333333331</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1087673906557995</v>
+        <v>-0.0672507389353143</v>
       </c>
       <c r="O8" t="n">
-        <v>1.97328670794704</v>
+        <v>6.26919540483344</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.000000000000003</v>
+        <v>10.43813333333333</v>
       </c>
       <c r="Q8" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-36.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2485278553085821</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1291339888921559</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>7.266666666666667</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X8" t="n">
-        <v>11.26666666666667</v>
+        <v>31.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.000000000000003</v>
+        <v>-1.616666666666671</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.323446270295476</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.05977432161476443</v>
+        <v>0.1615049145429354</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.233333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>-7.366666666666666</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.2739207603422623</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.033360466311896</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.7594397059696337</v>
+        <v>0.0881394731161023</v>
       </c>
       <c r="AO8" t="n">
-        <v>46.35</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="AP8" t="n">
-        <v>38.68333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.666666666666671</v>
+        <v>13.36666666666667</v>
       </c>
       <c r="AR8" t="n">
-        <v>38.07535235688084</v>
+        <v>36.80847059423598</v>
       </c>
       <c r="AS8" t="n">
-        <v>27.60990969505806</v>
+        <v>21.52025885865341</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.46544266182278</v>
+        <v>15.28821173558257</v>
       </c>
       <c r="AU8" t="n">
-        <v>32.55325</v>
+        <v>30.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>27.13333333333333</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.419916666666669</v>
+        <v>7.25</v>
       </c>
       <c r="AX8" t="n">
-        <v>26.21191049416226</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="AY8" t="n">
-        <v>19.99447365781878</v>
+        <v>17.06985215621225</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.217436836343481</v>
+        <v>7.825586979366491</v>
       </c>
       <c r="BA8" t="n">
-        <v>106.6166666666667</v>
+        <v>87.22195000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>120.7166666666667</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="BC8" t="n">
-        <v>-14.09999999999999</v>
+        <v>-47.16138333333329</v>
       </c>
       <c r="BD8" t="n">
-        <v>81.17353080024326</v>
+        <v>77.22913797862124</v>
       </c>
       <c r="BE8" t="n">
-        <v>97.0168296725888</v>
+        <v>102.738159054381</v>
       </c>
       <c r="BF8" t="n">
-        <v>-15.84329887234554</v>
+        <v>-25.50902107575976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2040,178 +2053,178 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_013_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>186.11555</v>
+        <v>219.9365833333333</v>
       </c>
       <c r="H9" t="n">
-        <v>221.15</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="I9" t="n">
-        <v>141.7178099447946</v>
+        <v>146.1177802267258</v>
       </c>
       <c r="J9" t="n">
-        <v>141.7137294264382</v>
+        <v>146.2265476173816</v>
       </c>
       <c r="K9" t="n">
-        <v>47.90276473827162</v>
+        <v>48.97751792605069</v>
       </c>
       <c r="L9" t="n">
-        <v>44.83512073701105</v>
+        <v>44.8576416936978</v>
       </c>
       <c r="M9" t="n">
-        <v>-35.03444999999999</v>
+        <v>-49.28008333333329</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004080518356403218</v>
+        <v>-0.1087673906557995</v>
       </c>
       <c r="O9" t="n">
-        <v>3.067644001260568</v>
+        <v>4.119876232352887</v>
       </c>
       <c r="P9" t="n">
-        <v>5.4</v>
+        <v>-31.04675</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>3.533333333333333</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.4</v>
+        <v>-40.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.5719741256040581</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1524231113411967</v>
+        <v>-0.1889083105069204</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>13.90325</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>9.853249999999999</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.189772290028397</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.637209221337241</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>-1.5</v>
+        <v>-7.366666666666666</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>0.2739207603422623</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.1164747371577703</v>
+        <v>1.033360466311896</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.1164747371577703</v>
+        <v>-0.7594397059696337</v>
       </c>
       <c r="AO9" t="n">
-        <v>45.23761666666667</v>
+        <v>46.35</v>
       </c>
       <c r="AP9" t="n">
-        <v>30.46666666666667</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.77095</v>
+        <v>7.666666666666671</v>
       </c>
       <c r="AR9" t="n">
-        <v>36.81108423008403</v>
+        <v>38.07535235688084</v>
       </c>
       <c r="AS9" t="n">
-        <v>21.5632715446163</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="AT9" t="n">
-        <v>15.24781268546773</v>
+        <v>10.46544266182278</v>
       </c>
       <c r="AU9" t="n">
-        <v>34.96666666666667</v>
+        <v>31.98333333333333</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AW9" t="n">
-        <v>11.96666666666667</v>
+        <v>5.166666666666661</v>
       </c>
       <c r="AX9" t="n">
-        <v>27.29337511764809</v>
+        <v>25.72295810760579</v>
       </c>
       <c r="AY9" t="n">
-        <v>17.07426318972899</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10.2191119279191</v>
+        <v>5.830029835698312</v>
       </c>
       <c r="BA9" t="n">
-        <v>96.97793333333334</v>
+        <v>93.28333333333333</v>
       </c>
       <c r="BB9" t="n">
-        <v>134.3833333333333</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BC9" t="n">
-        <v>-37.40539999999996</v>
+        <v>-23.69999999999997</v>
       </c>
       <c r="BD9" t="n">
-        <v>77.35417466541456</v>
+        <v>79.47271089677133</v>
       </c>
       <c r="BE9" t="n">
-        <v>102.738159054381</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BF9" t="n">
-        <v>-25.38398438896644</v>
+        <v>-17.0931010930376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2226,164 +2239,722 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_017_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>195.4022</v>
+        <v>186.11555</v>
       </c>
       <c r="H10" t="n">
-        <v>266.8632166666667</v>
+        <v>221.15</v>
       </c>
       <c r="I10" t="n">
-        <v>145.9064422742808</v>
+        <v>141.7178099447946</v>
       </c>
       <c r="J10" t="n">
-        <v>145.9943306994593</v>
+        <v>141.7137294264382</v>
       </c>
       <c r="K10" t="n">
-        <v>46.86485275946674</v>
+        <v>48.97984764694002</v>
       </c>
       <c r="L10" t="n">
-        <v>44.5741238531821</v>
+        <v>44.83512073701105</v>
       </c>
       <c r="M10" t="n">
-        <v>-71.46101666666669</v>
+        <v>-35.03444999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.08788842517850526</v>
+        <v>0.004080518356403218</v>
       </c>
       <c r="O10" t="n">
-        <v>2.290728906284642</v>
+        <v>4.14472690992897</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.333333333333336</v>
+        <v>-18.08873333333333</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2256049681381114</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2256049681381114</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>8.933333333333334</v>
       </c>
       <c r="X10" t="n">
-        <v>11.26666666666667</v>
+        <v>31.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.333333333333336</v>
+        <v>-22.86666666666667</v>
       </c>
       <c r="Z10" t="n">
         <v>0.2591759316479205</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.323446270295476</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.06427033864755549</v>
+        <v>0.03761503109371811</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.1164747371577703</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>45.07095</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.60428333333333</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>36.70010973267537</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>21.5632715446163</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>15.13683818805907</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>34.96666666666667</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>11.96666666666667</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>27.29337511764809</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>17.07426318972899</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.2191119279191</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>92.36666666666666</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-42.01666666666664</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>76.745440672119</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-25.992718382262</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>221.1224333333333</v>
+      </c>
+      <c r="H11" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="I11" t="n">
+        <v>141.8317368861638</v>
+      </c>
+      <c r="J11" t="n">
+        <v>141.6733980516045</v>
+      </c>
+      <c r="K11" t="n">
+        <v>49.27030586470386</v>
+      </c>
+      <c r="L11" t="n">
+        <v>44.82234079251659</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.02756666666670071</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1583388345593164</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.447965072187266</v>
+      </c>
+      <c r="P11" t="n">
+        <v>17.65075</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="X11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.4844248901091631</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.2215609005542024</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.2628639895549607</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.185676926950206</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.06920218979243568</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>58.60501666666666</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>28.13834999999999</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>43.70509198694462</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>21.5665214603954</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>22.13857052654922</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>31.31100557837641</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>17.03068189911616</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14.28032367926025</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>69.61666666666666</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-64.76666666666664</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>65.77016461009407</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-36.96799444428693</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>195.4022</v>
+      </c>
+      <c r="H12" t="n">
+        <v>266.8632166666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>145.9064422742808</v>
+      </c>
+      <c r="J12" t="n">
+        <v>145.9943306994593</v>
+      </c>
+      <c r="K12" t="n">
+        <v>48.03268705989514</v>
+      </c>
+      <c r="L12" t="n">
+        <v>45.34276468747346</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-71.46101666666669</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.08788842517850526</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.689922372421677</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-60.78113333333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8.933333333333334</v>
+      </c>
+      <c r="X12" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-62.14999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.2591759316479205</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5490512384335874</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.2898753067856669</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.418866666666667</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.368866666666667</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.7086331393992357</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1560700707080794</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>9.246550000000001</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK12" t="n">
         <v>-9.246550000000001</v>
       </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>0.8240664355600736</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN12" t="n">
         <v>-0.8240664355600736</v>
       </c>
-      <c r="AO10" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AO12" t="n">
+        <v>46.88333333333333</v>
+      </c>
+      <c r="AP12" t="n">
         <v>38.68333333333333</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>8.366666666666667</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>37.71427916549126</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AQ12" t="n">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>37.60330466808259</v>
+      </c>
+      <c r="AS12" t="n">
         <v>27.60990969505806</v>
       </c>
-      <c r="AT10" t="n">
-        <v>10.1043694704332</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AT12" t="n">
+        <v>9.993394973024532</v>
+      </c>
+      <c r="AU12" t="n">
         <v>35.66666666666666</v>
       </c>
-      <c r="AV10" t="n">
-        <v>27.13333333333333</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>8.533333333333328</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="AV12" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.849999999999987</v>
+      </c>
+      <c r="AX12" t="n">
         <v>27.74280476419689</v>
       </c>
-      <c r="AY10" t="n">
-        <v>19.99447365781878</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>7.74833110637811</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>103.7522</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>120.7166666666667</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>-16.9644666666667</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>80.19018241294468</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>97.0168296725888</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-16.82664725964412</v>
+      <c r="AY12" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7.849876492289411</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>116.9833333333333</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-18.48333333333331</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>79.5925237709541</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>96.56581198980894</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-16.97328821885483</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>255.7438833333333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>265.6299833333333</v>
+      </c>
+      <c r="I13" t="n">
+        <v>145.9773325040056</v>
+      </c>
+      <c r="J13" t="n">
+        <v>145.8893363990339</v>
+      </c>
+      <c r="K13" t="n">
+        <v>47.2452299004206</v>
+      </c>
+      <c r="L13" t="n">
+        <v>45.59497163487288</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-9.886100000000027</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.08799610497169397</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.65025826554772</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-3.295983333333339</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>45.16666666666666</v>
+      </c>
+      <c r="X13" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-25.91666666666667</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.6992727007011277</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5752841088710083</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.1239885918301193</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>26.67068333333333</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>22.62068333333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.4662856779261432</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.08627739076501301</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.883333333333333</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>7.683333333333334</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.2514853038814903</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.6833899734934139</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.4319046696119236</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>61.42319999999999</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>22.73986666666666</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>44.94924920648065</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>17.33933951142259</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>44.01666666666667</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>32.63164533881391</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12.73871706690643</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>75.58333333333333</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>117.3133166666667</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-41.72998333333337</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>66.97939427620221</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>96.5752612810128</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-29.59586700481059</v>
       </c>
     </row>
   </sheetData>
@@ -2397,46 +2968,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ev_time_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ice_time_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>time_diff_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ev_distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ice_distance_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>distance_diff_km</t>
         </is>
@@ -2445,7 +3016,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2457,25 +3028,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2487,25 +3058,25 @@
         <v>25.88333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>12.31666666666666</v>
+        <v>-43.60000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.3556868609874803</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2073716941169366</v>
+        <v>-0.4841912826215016</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2514,28 +3085,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.25</v>
+        <v>8.15</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.25</v>
+        <v>-1.799999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-1.222149598452762</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2565,7 +3136,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2574,28 +3145,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56.05</v>
+        <v>55.88333333333333</v>
       </c>
       <c r="D6" t="n">
         <v>25.13333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>30.91666666666667</v>
+        <v>30.75</v>
       </c>
       <c r="F6" t="n">
-        <v>44.91739841291827</v>
+        <v>44.7773945763174</v>
       </c>
       <c r="G6" t="n">
         <v>16.04368253659841</v>
       </c>
       <c r="H6" t="n">
-        <v>28.87371587631986</v>
+        <v>28.73371203971899</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2625,7 +3196,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2634,28 +3205,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>109.1269666666667</v>
+        <v>102.3936333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>154.5833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>-45.45636666666658</v>
+        <v>-42.2397</v>
       </c>
       <c r="F8" t="n">
-        <v>71.26833841096357</v>
+        <v>70.83249221561701</v>
       </c>
       <c r="G8" t="n">
-        <v>113.8863544926646</v>
+        <v>112.0883548622644</v>
       </c>
       <c r="H8" t="n">
-        <v>-42.61801608170103</v>
+        <v>-41.25586264664739</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2667,25 +3238,25 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2697,25 +3268,25 @@
         <v>25.88333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>3.533333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="E10" t="n">
-        <v>22.34999999999999</v>
+        <v>-5.916666666666671</v>
       </c>
       <c r="F10" t="n">
         <v>0.3556868609874803</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2489340406807565</v>
+        <v>0.1341259604332779</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2724,28 +3295,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.4693593484285414</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.4693593484285414</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2775,7 +3346,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2784,28 +3355,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>52.5</v>
+        <v>52.33333333333334</v>
       </c>
       <c r="D13" t="n">
         <v>30.46666666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>22.03333333333333</v>
+        <v>21.86666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>43.39133179794914</v>
+        <v>43.25132796134825</v>
       </c>
       <c r="G13" t="n">
         <v>21.52228685090974</v>
       </c>
       <c r="H13" t="n">
-        <v>21.8690449470394</v>
+        <v>21.72904111043851</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2835,7 +3406,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_002</t>
+          <t>PAIR_005</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2844,28 +3415,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>87.70028333333333</v>
+        <v>82.93361666666667</v>
       </c>
       <c r="D15" t="n">
         <v>134.3833333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>-46.68304999999997</v>
+        <v>-51.44971666666663</v>
       </c>
       <c r="F15" t="n">
-        <v>67.23643719629696</v>
+        <v>66.9070816844693</v>
       </c>
       <c r="G15" t="n">
         <v>102.738159054381</v>
       </c>
       <c r="H15" t="n">
-        <v>-35.50172185808404</v>
+        <v>-35.8310773699117</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2874,28 +3445,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-32.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1574257220881389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2904,28 +3475,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.266666666666667</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.300000000000003</v>
+        <v>-39.3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2993866064237053</v>
+        <v>-0.4568123285118442</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2934,28 +3505,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>14.29151666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4.341516666666671</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2.33611605697715</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.5381164265769423</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2985,7 +3556,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3015,7 +3586,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3024,28 +3595,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34.2</v>
+        <v>33.45</v>
       </c>
       <c r="D21" t="n">
         <v>23.43333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>10.76666666666667</v>
+        <v>10.01666666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>26.86273516629103</v>
+        <v>26.28668300273065</v>
       </c>
       <c r="G21" t="n">
         <v>16.77959665852362</v>
       </c>
       <c r="H21" t="n">
-        <v>10.08313850776741</v>
+        <v>9.507086344207032</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_003</t>
+          <t>PAIR_006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3054,28 +3625,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>106.9415166666667</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>154.5833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>-47.64181666666659</v>
+        <v>-51.23333333333329</v>
       </c>
       <c r="F22" t="n">
-        <v>82.12192653794388</v>
+        <v>80.36186264452711</v>
       </c>
       <c r="G22" t="n">
-        <v>113.9111543824703</v>
+        <v>112.1131547520701</v>
       </c>
       <c r="H22" t="n">
-        <v>-31.78922784452642</v>
+        <v>-31.75129210754299</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3087,25 +3658,25 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2440142861617139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3117,25 +3688,25 @@
         <v>29.40441666666667</v>
       </c>
       <c r="D24" t="n">
-        <v>11.26666666666667</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>18.13775</v>
+        <v>-41.67891666666666</v>
       </c>
       <c r="F24" t="n">
         <v>0.4715380269015641</v>
       </c>
       <c r="G24" t="n">
-        <v>0.323446270295476</v>
+        <v>0.56746055645719</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1480917566060881</v>
+        <v>-0.09592252955562586</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,28 +3715,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.770483333333333</v>
+        <v>9.237150000000002</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="E25" t="n">
-        <v>1.770483333333333</v>
+        <v>5.187150000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003326781778833682</v>
+        <v>0.7233426716155921</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="H25" t="n">
-        <v>0.003326781778833682</v>
+        <v>0.1707796029244358</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3195,7 +3766,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3204,28 +3775,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>55.21666666666667</v>
+        <v>55.05</v>
       </c>
       <c r="D27" t="n">
         <v>38.68333333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>16.53333333333334</v>
+        <v>16.36666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>44.51243008835447</v>
+        <v>44.37242625175359</v>
       </c>
       <c r="G27" t="n">
         <v>27.60990969505806</v>
       </c>
       <c r="H27" t="n">
-        <v>16.90252039329641</v>
+        <v>16.76251655669553</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3237,25 +3808,25 @@
         <v>38.85</v>
       </c>
       <c r="D28" t="n">
-        <v>27.13333333333333</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="E28" t="n">
-        <v>11.71666666666667</v>
+        <v>12.03333333333333</v>
       </c>
       <c r="F28" t="n">
         <v>30.69503766819436</v>
       </c>
       <c r="G28" t="n">
-        <v>19.99447365781878</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="H28" t="n">
-        <v>10.70056401037558</v>
+        <v>10.80210939628688</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_004</t>
+          <t>PAIR_007</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3264,28 +3835,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>99.63333333333334</v>
+        <v>92.33333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>120.7166666666667</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>-21.08333333333336</v>
+        <v>-24.64999999999998</v>
       </c>
       <c r="F29" t="n">
-        <v>69.80145446689757</v>
+        <v>69.22144241366169</v>
       </c>
       <c r="G29" t="n">
-        <v>97.0168296725888</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="H29" t="n">
-        <v>-27.21537520569123</v>
+        <v>-27.34436957614724</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,25 +3868,25 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3327,25 +3898,25 @@
         <v>12.03333333333333</v>
       </c>
       <c r="D31" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.53333333333334</v>
+        <v>-57.45</v>
       </c>
       <c r="F31" t="n">
         <v>0.3736603870816042</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1893981680228127</v>
+        <v>-0.4662177565273777</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3354,28 +3925,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-5.199999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.7015215125621636</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-1.096478117838044</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3405,7 +3976,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3435,7 +4006,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3465,7 +4036,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAIR_005</t>
+          <t>PAIR_008</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3474,28 +4045,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>105.2968</v>
+        <v>100.5468</v>
       </c>
       <c r="D36" t="n">
-        <v>153.4</v>
+        <v>143.45</v>
       </c>
       <c r="E36" t="n">
-        <v>-48.1032</v>
+        <v>-42.90319999999998</v>
       </c>
       <c r="F36" t="n">
-        <v>82.21470927818682</v>
+        <v>81.51318776562465</v>
       </c>
       <c r="G36" t="n">
-        <v>113.6030563965588</v>
+        <v>111.8050567661586</v>
       </c>
       <c r="H36" t="n">
-        <v>-31.38834711837198</v>
+        <v>-30.29186900053395</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3504,28 +4075,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.349999999999998</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0045857861689476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3534,28 +4105,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7.266666666666667</v>
+        <v>35.56666666666667</v>
       </c>
       <c r="D38" t="n">
-        <v>3.533333333333333</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="E38" t="n">
-        <v>3.733333333333333</v>
+        <v>-33.91666666666666</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.5933262321891101</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1569191283739878</v>
+        <v>-0.2465519114198719</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3564,28 +4135,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>26.16571666666666</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>16.21571666666666</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.5067319571443681</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-1.29126767325584</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3594,28 +4165,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="D40" t="n">
-        <v>1.5</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.3333333333333328</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2046142102738726</v>
+        <v>0.1799078409944621</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0881394731161023</v>
+        <v>-0.396000011716256</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3624,28 +4195,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>43.83333333333334</v>
+        <v>63.03526666666667</v>
       </c>
       <c r="D41" t="n">
-        <v>30.46666666666667</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="E41" t="n">
-        <v>13.36666666666667</v>
+        <v>37.90193333333335</v>
       </c>
       <c r="F41" t="n">
-        <v>36.80847059423598</v>
+        <v>45.7896379485424</v>
       </c>
       <c r="G41" t="n">
-        <v>21.52025885865341</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="H41" t="n">
-        <v>15.28821173558257</v>
+        <v>29.74595541194399</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3654,28 +4225,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>30.75</v>
+        <v>45.45</v>
       </c>
       <c r="D42" t="n">
-        <v>23</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="E42" t="n">
-        <v>7.75</v>
+        <v>22.01666666666667</v>
       </c>
       <c r="F42" t="n">
-        <v>25.36797775428393</v>
+        <v>33.36307095293761</v>
       </c>
       <c r="G42" t="n">
-        <v>17.06985215621225</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="H42" t="n">
-        <v>8.298125598071682</v>
+        <v>16.58347429441399</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_009</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3684,28 +4255,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>98.77674999999999</v>
+        <v>75</v>
       </c>
       <c r="D43" t="n">
-        <v>134.3833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="E43" t="n">
-        <v>-35.6065833333333</v>
+        <v>-69.6333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>78.83492659413233</v>
+        <v>67.97543734942298</v>
       </c>
       <c r="G43" t="n">
-        <v>102.738159054381</v>
+        <v>112.1322772301322</v>
       </c>
       <c r="H43" t="n">
-        <v>-23.90323246024867</v>
+        <v>-44.15683988070923</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3714,28 +4285,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-36.9</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2485278553085821</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1291339888921559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3744,28 +4315,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7.266666666666667</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>11.26666666666667</v>
+        <v>31.8</v>
       </c>
       <c r="E45" t="n">
-        <v>-4.000000000000003</v>
+        <v>-1.616666666666671</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="G45" t="n">
-        <v>0.323446270295476</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.05977432161476443</v>
+        <v>0.1615049145429354</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3774,28 +4345,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3804,28 +4375,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.233333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="D47" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="E47" t="n">
-        <v>-7.366666666666666</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2739207603422623</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="G47" t="n">
-        <v>1.033360466311896</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.7594397059696337</v>
+        <v>0.0881394731161023</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3834,28 +4405,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>46.35</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="D48" t="n">
-        <v>38.68333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="E48" t="n">
-        <v>7.666666666666671</v>
+        <v>13.36666666666667</v>
       </c>
       <c r="F48" t="n">
-        <v>38.07535235688084</v>
+        <v>36.80847059423598</v>
       </c>
       <c r="G48" t="n">
-        <v>27.60990969505806</v>
+        <v>21.52025885865341</v>
       </c>
       <c r="H48" t="n">
-        <v>10.46544266182278</v>
+        <v>15.28821173558257</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3864,28 +4435,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>32.55325</v>
+        <v>30.25</v>
       </c>
       <c r="D49" t="n">
-        <v>27.13333333333333</v>
+        <v>23</v>
       </c>
       <c r="E49" t="n">
-        <v>5.419916666666669</v>
+        <v>7.25</v>
       </c>
       <c r="F49" t="n">
-        <v>26.21191049416226</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="G49" t="n">
-        <v>19.99447365781878</v>
+        <v>17.06985215621225</v>
       </c>
       <c r="H49" t="n">
-        <v>6.217436836343481</v>
+        <v>7.825586979366491</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAIR_012</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3894,28 +4465,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>106.6166666666667</v>
+        <v>87.22195000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>120.7166666666667</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="E50" t="n">
-        <v>-14.09999999999999</v>
+        <v>-47.16138333333329</v>
       </c>
       <c r="F50" t="n">
-        <v>81.17353080024326</v>
+        <v>77.22913797862124</v>
       </c>
       <c r="G50" t="n">
-        <v>97.0168296725888</v>
+        <v>102.738159054381</v>
       </c>
       <c r="H50" t="n">
-        <v>-15.84329887234554</v>
+        <v>-25.50902107575976</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3927,25 +4498,25 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3954,28 +4525,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="D52" t="n">
-        <v>3.533333333333333</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="E52" t="n">
-        <v>5.4</v>
+        <v>-40.9</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.5719741256040581</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1524231113411967</v>
+        <v>-0.1889083105069204</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3984,28 +4555,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>13.90325</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>9.853249999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2.189772290028397</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1.637209221337241</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4014,28 +4585,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="D54" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.5</v>
+        <v>-7.366666666666666</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.2739207603422623</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1164747371577703</v>
+        <v>1.033360466311896</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1164747371577703</v>
+        <v>-0.7594397059696337</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4044,28 +4615,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>45.23761666666667</v>
+        <v>46.35</v>
       </c>
       <c r="D55" t="n">
-        <v>30.46666666666667</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="E55" t="n">
-        <v>14.77095</v>
+        <v>7.666666666666671</v>
       </c>
       <c r="F55" t="n">
-        <v>36.81108423008403</v>
+        <v>38.07535235688084</v>
       </c>
       <c r="G55" t="n">
-        <v>21.5632715446163</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="H55" t="n">
-        <v>15.24781268546773</v>
+        <v>10.46544266182278</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4074,28 +4645,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>34.96666666666667</v>
+        <v>31.98333333333333</v>
       </c>
       <c r="D56" t="n">
-        <v>23</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="E56" t="n">
-        <v>11.96666666666667</v>
+        <v>5.166666666666661</v>
       </c>
       <c r="F56" t="n">
-        <v>27.29337511764809</v>
+        <v>25.72295810760579</v>
       </c>
       <c r="G56" t="n">
-        <v>17.07426318972899</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="H56" t="n">
-        <v>10.2191119279191</v>
+        <v>5.830029835698312</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAIR_013</t>
+          <t>PAIR_017</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4104,28 +4675,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>96.97793333333334</v>
+        <v>93.28333333333333</v>
       </c>
       <c r="D57" t="n">
-        <v>134.3833333333333</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="E57" t="n">
-        <v>-37.40539999999996</v>
+        <v>-23.69999999999997</v>
       </c>
       <c r="F57" t="n">
-        <v>77.35417466541456</v>
+        <v>79.47271089677133</v>
       </c>
       <c r="G57" t="n">
-        <v>102.738159054381</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="H57" t="n">
-        <v>-25.38398438896644</v>
+        <v>-17.0931010930376</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4137,25 +4708,25 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2256049681381114</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.2256049681381114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4167,25 +4738,25 @@
         <v>8.933333333333334</v>
       </c>
       <c r="D59" t="n">
-        <v>11.26666666666667</v>
+        <v>31.8</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.333333333333336</v>
+        <v>-22.86666666666667</v>
       </c>
       <c r="F59" t="n">
         <v>0.2591759316479205</v>
       </c>
       <c r="G59" t="n">
-        <v>0.323446270295476</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.06427033864755549</v>
+        <v>0.03761503109371811</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4194,28 +4765,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.7197084907042335</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4227,25 +4798,25 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>9.246550000000001</v>
+        <v>1.5</v>
       </c>
       <c r="E61" t="n">
-        <v>-9.246550000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8240664355600736</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.8240664355600736</v>
+        <v>-0.1164747371577703</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4254,28 +4825,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>47.05</v>
+        <v>45.07095</v>
       </c>
       <c r="D62" t="n">
-        <v>38.68333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="E62" t="n">
-        <v>8.366666666666667</v>
+        <v>14.60428333333333</v>
       </c>
       <c r="F62" t="n">
-        <v>37.71427916549126</v>
+        <v>36.70010973267537</v>
       </c>
       <c r="G62" t="n">
-        <v>27.60990969505806</v>
+        <v>21.5632715446163</v>
       </c>
       <c r="H62" t="n">
-        <v>10.1043694704332</v>
+        <v>15.13683818805907</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4284,28 +4855,28 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>35.66666666666666</v>
+        <v>34.96666666666667</v>
       </c>
       <c r="D63" t="n">
-        <v>27.13333333333333</v>
+        <v>23</v>
       </c>
       <c r="E63" t="n">
-        <v>8.533333333333328</v>
+        <v>11.96666666666667</v>
       </c>
       <c r="F63" t="n">
-        <v>27.74280476419689</v>
+        <v>27.29337511764809</v>
       </c>
       <c r="G63" t="n">
-        <v>19.99447365781878</v>
+        <v>17.07426318972899</v>
       </c>
       <c r="H63" t="n">
-        <v>7.74833110637811</v>
+        <v>10.2191119279191</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4314,22 +4885,652 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>103.7522</v>
+        <v>92.36666666666666</v>
       </c>
       <c r="D64" t="n">
-        <v>120.7166666666667</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="E64" t="n">
-        <v>-16.9644666666667</v>
+        <v>-42.01666666666664</v>
       </c>
       <c r="F64" t="n">
-        <v>80.19018241294468</v>
+        <v>76.745440672119</v>
       </c>
       <c r="G64" t="n">
-        <v>97.0168296725888</v>
+        <v>102.738159054381</v>
       </c>
       <c r="H64" t="n">
-        <v>-16.82664725964412</v>
+        <v>-25.992718382262</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="D66" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.4844248901091631</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.2215609005542024</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.2628639895549607</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.185676926950206</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.06920218979243568</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>58.60501666666666</v>
+      </c>
+      <c r="D69" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="E69" t="n">
+        <v>28.13834999999999</v>
+      </c>
+      <c r="F69" t="n">
+        <v>43.70509198694462</v>
+      </c>
+      <c r="G69" t="n">
+        <v>21.5665214603954</v>
+      </c>
+      <c r="H69" t="n">
+        <v>22.13857052654922</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="D70" t="n">
+        <v>23</v>
+      </c>
+      <c r="E70" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="F70" t="n">
+        <v>31.31100557837641</v>
+      </c>
+      <c r="G70" t="n">
+        <v>17.03068189911616</v>
+      </c>
+      <c r="H70" t="n">
+        <v>14.28032367926025</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>69.61666666666666</v>
+      </c>
+      <c r="D71" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-64.76666666666664</v>
+      </c>
+      <c r="F71" t="n">
+        <v>65.77016461009407</v>
+      </c>
+      <c r="G71" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-36.96799444428693</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>8.933333333333334</v>
+      </c>
+      <c r="D73" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-62.14999999999999</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.2591759316479205</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.5490512384335874</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0.2898753067856669</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>5.418866666666667</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.368866666666667</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.7086331393992357</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.1560700707080794</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9.246550000000001</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-9.246550000000001</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.8240664355600736</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0.8240664355600736</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>46.88333333333333</v>
+      </c>
+      <c r="D76" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="E76" t="n">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="F76" t="n">
+        <v>37.60330466808259</v>
+      </c>
+      <c r="G76" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="H76" t="n">
+        <v>9.993394973024532</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>35.66666666666666</v>
+      </c>
+      <c r="D77" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="E77" t="n">
+        <v>8.849999999999987</v>
+      </c>
+      <c r="F77" t="n">
+        <v>27.74280476419689</v>
+      </c>
+      <c r="G77" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7.849876492289411</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>116.9833333333333</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-18.48333333333331</v>
+      </c>
+      <c r="F78" t="n">
+        <v>79.5925237709541</v>
+      </c>
+      <c r="G78" t="n">
+        <v>96.56581198980894</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-16.97328821885483</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>45.16666666666666</v>
+      </c>
+      <c r="D80" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-25.91666666666667</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.6992727007011277</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.5752841088710083</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.1239885918301193</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>26.67068333333333</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E81" t="n">
+        <v>22.62068333333333</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.4662856779261432</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.08627739076501301</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2.883333333333333</v>
+      </c>
+      <c r="D82" t="n">
+        <v>7.683333333333334</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.2514853038814903</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.6833899734934139</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.4319046696119236</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>61.42319999999999</v>
+      </c>
+      <c r="D83" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="E83" t="n">
+        <v>22.73986666666666</v>
+      </c>
+      <c r="F83" t="n">
+        <v>44.94924920648065</v>
+      </c>
+      <c r="G83" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="H83" t="n">
+        <v>17.33933951142259</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>44.01666666666667</v>
+      </c>
+      <c r="D84" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="E84" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>32.63164533881391</v>
+      </c>
+      <c r="G84" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="H84" t="n">
+        <v>12.73871706690643</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>75.58333333333333</v>
+      </c>
+      <c r="D85" t="n">
+        <v>117.3133166666667</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-41.72998333333337</v>
+      </c>
+      <c r="F85" t="n">
+        <v>66.97939427620221</v>
+      </c>
+      <c r="G85" t="n">
+        <v>96.5752612810128</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-29.59586700481059</v>
       </c>
     </row>
   </sheetData>
@@ -4347,37 +5548,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>EV_Mean_Time_min</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ICE_Mean_Time_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_Time_Diff_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Median_Time_Diff_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>EV_Mean_Distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ICE_Mean_Distance_km</t>
         </is>
@@ -4390,22 +5591,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.63888888888889</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-40.36111111111111</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-36.9</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03979795547214207</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2103366795405043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4415,22 +5616,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.7634537037037</v>
+        <v>26.06842361111111</v>
       </c>
       <c r="C3" t="n">
-        <v>9.455555555555557</v>
+        <v>57.45555555555556</v>
       </c>
       <c r="D3" t="n">
-        <v>5.307898148148145</v>
+        <v>-31.38713194444444</v>
       </c>
       <c r="E3" t="n">
-        <v>3.733333333333333</v>
+        <v>-36.60833333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3184377605884561</v>
+        <v>0.416762105628732</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3310858819022056</v>
+        <v>0.5424605171682151</v>
       </c>
     </row>
     <row r="4">
@@ -4440,22 +5641,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3356092592592592</v>
+        <v>12.44477777777778</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3356092592592592</v>
+        <v>7.778111111111111</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5.060241666666668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0003696424198704091</v>
+        <v>0.9875851087199073</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.7835208996971215</v>
       </c>
     </row>
     <row r="5">
@@ -4465,22 +5666,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.377777777777778</v>
+        <v>3.136111111111111</v>
       </c>
       <c r="C5" t="n">
-        <v>4.627394444444445</v>
+        <v>4.378879166666667</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.249616666666667</v>
+        <v>-1.242768055555556</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.266666666666667</v>
+        <v>-0.4666666666666671</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2547561477631287</v>
+        <v>0.2424896168078597</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5366391693100899</v>
+        <v>0.5171270905960592</v>
       </c>
     </row>
     <row r="6">
@@ -4490,22 +5691,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.02553888888889</v>
+        <v>51.95500000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>31.4269</v>
+        <v>31.42711944444444</v>
       </c>
       <c r="D6" t="n">
-        <v>17.59863888888889</v>
+        <v>20.52788055555556</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53333333333334</v>
+        <v>21.82061666666667</v>
       </c>
       <c r="F6" t="n">
-        <v>39.83041884252065</v>
+        <v>41.02298235166946</v>
       </c>
       <c r="G6" t="n">
-        <v>21.72994439358199</v>
+        <v>21.73246776952415</v>
       </c>
     </row>
     <row r="7">
@@ -4515,22 +5716,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.58091296296296</v>
+        <v>37.41874722222222</v>
       </c>
       <c r="C7" t="n">
-        <v>24.52222222222222</v>
+        <v>24.41666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>11.05869074074074</v>
+        <v>13.00208055555556</v>
       </c>
       <c r="E7" t="n">
-        <v>11.71666666666667</v>
+        <v>12.075</v>
       </c>
       <c r="F7" t="n">
-        <v>28.12192345936337</v>
+        <v>29.07212415296469</v>
       </c>
       <c r="G7" t="n">
-        <v>17.94877215980477</v>
+        <v>17.91146000917136</v>
       </c>
     </row>
     <row r="8">
@@ -4540,22 +5741,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101.6469388888889</v>
+        <v>88.59827777777777</v>
       </c>
       <c r="C8" t="n">
-        <v>136.4296296296296</v>
+        <v>131.9288875</v>
       </c>
       <c r="D8" t="n">
-        <v>-34.78269074074072</v>
+        <v>-43.3306097222222</v>
       </c>
       <c r="E8" t="n">
-        <v>-37.40539999999996</v>
+        <v>-42.57144999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>76.68840892922485</v>
+        <v>73.55007302317372</v>
       </c>
       <c r="G8" t="n">
-        <v>104.5183923836226</v>
+        <v>103.7803480898824</v>
       </c>
     </row>
   </sheetData>
@@ -4573,47 +5774,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>std</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>max</t>
         </is>
@@ -4626,28 +5827,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>7.555555555555555</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>5.74697988318889</v>
+        <v>7.51765598542202</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>18.25</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -4657,28 +5858,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>212.3691203703704</v>
+        <v>219.6213375</v>
       </c>
       <c r="D3" t="n">
-        <v>17.81452248709791</v>
+        <v>21.49761037932515</v>
       </c>
       <c r="E3" t="n">
         <v>186.11555</v>
       </c>
       <c r="F3" t="n">
-        <v>199.7801333333333</v>
+        <v>204.1775958333334</v>
       </c>
       <c r="G3" t="n">
-        <v>209.5919166666667</v>
+        <v>220.5295083333333</v>
       </c>
       <c r="H3" t="n">
-        <v>221.5170833333333</v>
+        <v>234.7795833333333</v>
       </c>
       <c r="I3" t="n">
-        <v>240.4436333333333</v>
+        <v>255.7438833333333</v>
       </c>
     </row>
     <row r="4">
@@ -4688,13 +5889,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>254.4617018518519</v>
+        <v>254.273775</v>
       </c>
       <c r="D4" t="n">
-        <v>25.10544802600185</v>
+        <v>24.62775367421587</v>
       </c>
       <c r="E4" t="n">
         <v>221.15</v>
@@ -4703,10 +5904,10 @@
         <v>221.15</v>
       </c>
       <c r="G4" t="n">
-        <v>269.2166666666666</v>
+        <v>268.0399416666667</v>
       </c>
       <c r="H4" t="n">
-        <v>272.7087666666667</v>
+        <v>273.119075</v>
       </c>
       <c r="I4" t="n">
         <v>274.35</v>
@@ -4719,28 +5920,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>145.2541127373525</v>
+        <v>145.2920163589644</v>
       </c>
       <c r="D5" t="n">
-        <v>2.847689428239811</v>
+        <v>2.8129708792688</v>
       </c>
       <c r="E5" t="n">
         <v>141.5990549680233</v>
       </c>
       <c r="F5" t="n">
-        <v>141.7178099447946</v>
+        <v>141.8032551508215</v>
       </c>
       <c r="G5" t="n">
-        <v>146.1103622297162</v>
+        <v>146.0438473668609</v>
       </c>
       <c r="H5" t="n">
-        <v>147.8063808897662</v>
+        <v>147.904477923269</v>
       </c>
       <c r="I5" t="n">
-        <v>148.208411945328</v>
+        <v>148.4081122812309</v>
       </c>
     </row>
     <row r="6">
@@ -4750,28 +5951,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>145.2751706677622</v>
+        <v>145.2673843760393</v>
       </c>
       <c r="D6" t="n">
-        <v>2.815206076441016</v>
+        <v>2.781898436675304</v>
       </c>
       <c r="E6" t="n">
         <v>141.6663057069586</v>
       </c>
       <c r="F6" t="n">
-        <v>141.7137294264382</v>
+        <v>141.7036465827298</v>
       </c>
       <c r="G6" t="n">
-        <v>146.1941703909393</v>
+        <v>146.0942505451993</v>
       </c>
       <c r="H6" t="n">
-        <v>147.7347082243865</v>
+        <v>147.8323860893165</v>
       </c>
       <c r="I6" t="n">
-        <v>148.150219573912</v>
+        <v>148.1693420519742</v>
       </c>
     </row>
     <row r="7">
@@ -4781,28 +5982,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>45.96155551613413</v>
+        <v>47.78934717098331</v>
       </c>
       <c r="D7" t="n">
-        <v>2.170136290808141</v>
+        <v>2.194246102296493</v>
       </c>
       <c r="E7" t="n">
-        <v>41.58535677727425</v>
+        <v>42.80810564129094</v>
       </c>
       <c r="F7" t="n">
-        <v>46.08133386225383</v>
+        <v>47.25168896860315</v>
       </c>
       <c r="G7" t="n">
-        <v>46.35627936949886</v>
+        <v>48.0710590752668</v>
       </c>
       <c r="H7" t="n">
-        <v>47.1164527446597</v>
+        <v>49.05246220138098</v>
       </c>
       <c r="I7" t="n">
-        <v>48.28995397818726</v>
+        <v>51.08928882117495</v>
       </c>
     </row>
     <row r="8">
@@ -4812,28 +6013,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>44.1007710985912</v>
+        <v>44.94682319696793</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7231356933532274</v>
+        <v>0.2586388852712208</v>
       </c>
       <c r="E8" t="n">
-        <v>43.13601932523515</v>
+        <v>44.7845362014835</v>
       </c>
       <c r="F8" t="n">
-        <v>43.36902945799262</v>
+        <v>44.81458420079127</v>
       </c>
       <c r="G8" t="n">
-        <v>44.10804715430679</v>
+        <v>44.82873076476382</v>
       </c>
       <c r="H8" t="n">
-        <v>44.82009341634151</v>
+        <v>44.90411641857893</v>
       </c>
       <c r="I8" t="n">
-        <v>44.83512073701105</v>
+        <v>45.59497163487288</v>
       </c>
     </row>
     <row r="9">
@@ -4843,28 +6044,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>-42.0925814814815</v>
+        <v>-34.65243750000002</v>
       </c>
       <c r="D9" t="n">
-        <v>21.70728020772361</v>
+        <v>23.62088669813258</v>
       </c>
       <c r="E9" t="n">
         <v>-72.92863333333338</v>
       </c>
       <c r="F9" t="n">
-        <v>-52.83291666666673</v>
+        <v>-50.16829166666665</v>
       </c>
       <c r="G9" t="n">
-        <v>-36.32509999999999</v>
+        <v>-34.47040833333335</v>
       </c>
       <c r="H9" t="n">
-        <v>-33.90636666666671</v>
+        <v>-14.51945833333331</v>
       </c>
       <c r="I9" t="n">
-        <v>-11.55808333333331</v>
+        <v>-0.02756666666670071</v>
       </c>
     </row>
     <row r="10">
@@ -4874,28 +6075,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.02105793040962883</v>
+        <v>0.0246319829250865</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07368965683920681</v>
+        <v>0.1087019112084609</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1087673906557995</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.08380816122308943</v>
+        <v>-0.07139009450725808</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04910155251721449</v>
+        <v>0.03113644488620082</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05819237141599842</v>
+        <v>0.07701103099631013</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07334933967118218</v>
+        <v>0.2387702292566871</v>
       </c>
     </row>
     <row r="11">
@@ -4905,28 +6106,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>1.860784417542917</v>
+        <v>2.842523974015379</v>
       </c>
       <c r="D11" t="n">
-        <v>1.888883295007344</v>
+        <v>2.21385178372173</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.550662547960897</v>
+        <v>-1.976430560192554</v>
       </c>
       <c r="F11" t="n">
-        <v>1.31656205477654</v>
+        <v>2.236735495546228</v>
       </c>
       <c r="G11" t="n">
-        <v>2.290728906284642</v>
+        <v>2.952793577434512</v>
       </c>
       <c r="H11" t="n">
-        <v>3.212996815879364</v>
+        <v>4.220536450493544</v>
       </c>
       <c r="I11" t="n">
-        <v>3.747423286667086</v>
+        <v>6.26919540483344</v>
       </c>
     </row>
     <row r="12">
@@ -4936,28 +6137,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>5.643507407407405</v>
+        <v>-23.60902083333334</v>
       </c>
       <c r="D12" t="n">
-        <v>10.60574991169331</v>
+        <v>26.25470265736834</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.300000000000003</v>
+        <v>-62.65000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.333333333333336</v>
+        <v>-38.718825</v>
       </c>
       <c r="G12" t="n">
-        <v>3.733333333333333</v>
+        <v>-24.56774166666666</v>
       </c>
       <c r="H12" t="n">
-        <v>13.56666666666666</v>
+        <v>-2.717820833333339</v>
       </c>
       <c r="I12" t="n">
-        <v>22.34999999999999</v>
+        <v>17.65075</v>
       </c>
     </row>
     <row r="13">
@@ -4967,13 +6168,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.63888888888889</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>11.45833333333334</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4985,10 +6186,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4998,28 +6199,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>47.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>14.89603554641301</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5029,28 +6230,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>-40.36111111111111</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>18.79322425178228</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-36.9</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.349999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5060,13 +6261,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0.03979795547214207</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0596969332082131</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -5078,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5091,28 +6292,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2103366795405043</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07370798729837066</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5122,28 +6323,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1705387240683622</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09340028109880034</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2440142861617139</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1574257220881389</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0045857861689476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5153,28 +6354,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>14.7634537037037</v>
+        <v>26.06842361111111</v>
       </c>
       <c r="D19" t="n">
-        <v>9.392156663784304</v>
+        <v>10.95654748309503</v>
       </c>
       <c r="E19" t="n">
-        <v>7.266666666666667</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>7.266666666666667</v>
+        <v>22.42083333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>8.933333333333334</v>
+        <v>29.793875</v>
       </c>
       <c r="H19" t="n">
-        <v>25.88333333333333</v>
+        <v>30.25416666666666</v>
       </c>
       <c r="I19" t="n">
-        <v>29.40441666666667</v>
+        <v>45.16666666666666</v>
       </c>
     </row>
     <row r="20">
@@ -5184,28 +6385,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>9.455555555555556</v>
+        <v>57.45555555555556</v>
       </c>
       <c r="D20" t="n">
-        <v>4.55195318273132</v>
+        <v>18.96016202746548</v>
       </c>
       <c r="E20" t="n">
-        <v>3.533333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.533333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="G20" t="n">
-        <v>11.26666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>13.56666666666667</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>13.56666666666667</v>
+        <v>71.08333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -5215,28 +6416,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>5.307898148148146</v>
+        <v>-31.38713194444444</v>
       </c>
       <c r="D21" t="n">
-        <v>10.20551346952703</v>
+        <v>20.40719378685777</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.300000000000003</v>
+        <v>-62.14999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.333333333333336</v>
+        <v>-42.15918749999999</v>
       </c>
       <c r="G21" t="n">
-        <v>3.733333333333333</v>
+        <v>-36.60833333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>12.31666666666666</v>
+        <v>-18.62916666666667</v>
       </c>
       <c r="I21" t="n">
-        <v>22.34999999999999</v>
+        <v>-1.333333333333332</v>
       </c>
     </row>
     <row r="22">
@@ -5246,28 +6447,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3184377605884561</v>
+        <v>0.4167621056287321</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07523798258153712</v>
+        <v>0.1282600464522988</v>
       </c>
       <c r="E22" t="n">
         <v>0.2591759316479205</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3556868609874803</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3556868609874803</v>
+        <v>0.4747597427034639</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4715380269015641</v>
+        <v>0.6992727007011277</v>
       </c>
     </row>
     <row r="23">
@@ -5277,28 +6478,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3310858819022056</v>
+        <v>0.542460517168215</v>
       </c>
       <c r="D23" t="n">
-        <v>0.197669238220269</v>
+        <v>0.2642918694221398</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="G23" t="n">
-        <v>0.323446270295476</v>
+        <v>0.569717341030624</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
     </row>
     <row r="24">
@@ -5308,28 +6509,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0126481213137495</v>
+        <v>-0.1256984115394831</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1957442973567837</v>
+        <v>0.268080513568443</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2993866064237053</v>
+        <v>-0.4841912826215016</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1893981680228127</v>
+        <v>-0.3316095622172112</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.05977432161476443</v>
+        <v>-0.1424154200312731</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1524231113411967</v>
+        <v>0.126522933980909</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2489340406807565</v>
+        <v>0.2628639895549607</v>
       </c>
     </row>
     <row r="25">
@@ -5339,28 +6540,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3356092592592592</v>
+        <v>12.44477777777778</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6785470745926708</v>
+        <v>7.929244283147984</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5.297483333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>10.645975</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>15.46465833333334</v>
       </c>
       <c r="I25" t="n">
-        <v>1.770483333333333</v>
+        <v>26.67068333333333</v>
       </c>
     </row>
     <row r="26">
@@ -5370,13 +6571,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>4.666666666666666</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4.267069109808134</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -5385,13 +6586,13 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -5401,28 +6602,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3356092592592592</v>
+        <v>7.778111111111111</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6785470745926708</v>
+        <v>8.40201438706343</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-5.199999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3.59835416666667</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5.060241666666668</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>13.09502916666667</v>
       </c>
       <c r="I27" t="n">
-        <v>1.770483333333333</v>
+        <v>22.62068333333333</v>
       </c>
     </row>
     <row r="28">
@@ -5432,28 +6633,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0003696424198704091</v>
+        <v>0.9875851087199073</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001108927259611227</v>
+        <v>0.7428811852973265</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.3753728936893338</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.4973888049654114</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.7050773259806996</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.062088812265765</v>
       </c>
       <c r="I28" t="n">
-        <v>0.003326781778833682</v>
+        <v>2.33611605697715</v>
       </c>
     </row>
     <row r="29">
@@ -5463,13 +6664,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.7835208996971215</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.7854156085709972</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5478,13 +6679,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
     </row>
     <row r="30">
@@ -5494,28 +6695,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003696424198704091</v>
+        <v>0.2040642090227859</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001108927259611227</v>
+        <v>1.048514002736508</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-1.29126767325584</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.3388275725332709</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.2730762483068848</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.5835144426087651</v>
       </c>
       <c r="I30" t="n">
-        <v>0.003326781778833682</v>
+        <v>2.078327234216284</v>
       </c>
     </row>
     <row r="31">
@@ -5525,25 +6726,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" t="n">
-        <v>3.377777777777778</v>
+        <v>3.136111111111111</v>
       </c>
       <c r="D31" t="n">
-        <v>3.312759423803667</v>
+        <v>2.864567883337583</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.5375</v>
       </c>
       <c r="G31" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H31" t="n">
-        <v>5.933333333333334</v>
+        <v>4.658333333333333</v>
       </c>
       <c r="I31" t="n">
         <v>8.016666666666667</v>
@@ -5556,13 +6757,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>4.627394444444445</v>
+        <v>4.378879166666667</v>
       </c>
       <c r="D32" t="n">
-        <v>4.69244081123507</v>
+        <v>4.295902727823979</v>
       </c>
       <c r="E32" t="n">
         <v>1.266666666666667</v>
@@ -5574,7 +6775,7 @@
         <v>1.716666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>9.246550000000001</v>
+        <v>8.074137500000001</v>
       </c>
       <c r="I32" t="n">
         <v>11.6</v>
@@ -5587,25 +6788,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.249616666666667</v>
+        <v>-1.242768055555556</v>
       </c>
       <c r="D33" t="n">
-        <v>5.028154475909736</v>
+        <v>4.488065159383455</v>
       </c>
       <c r="E33" t="n">
         <v>-9.246550000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.583333333333332</v>
+        <v>-3.887499999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.266666666666667</v>
+        <v>-0.4666666666666671</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="I33" t="n">
         <v>6.300000000000001</v>
@@ -5618,25 +6819,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2547561477631287</v>
+        <v>0.2424896168078597</v>
       </c>
       <c r="D34" t="n">
-        <v>0.246715825544023</v>
+        <v>0.212245330049233</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.1349308807458466</v>
       </c>
       <c r="G34" t="n">
         <v>0.2046142102738726</v>
       </c>
       <c r="H34" t="n">
-        <v>0.356505753799326</v>
+        <v>0.2945670087065282</v>
       </c>
       <c r="I34" t="n">
         <v>0.6265751975894123</v>
@@ -5649,13 +6850,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5366391693100899</v>
+        <v>0.5171270905960593</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3685988024017844</v>
+        <v>0.3413832744129097</v>
       </c>
       <c r="E35" t="n">
         <v>0.1164747371577703</v>
@@ -5667,7 +6868,7 @@
         <v>0.5759078527107181</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8240664355600736</v>
+        <v>0.7185590890100788</v>
       </c>
       <c r="I35" t="n">
         <v>1.033360466311896</v>
@@ -5680,25 +6881,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2818830215469612</v>
+        <v>-0.2746374737881995</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3742396279795544</v>
+        <v>0.3409348678945429</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8240664355600736</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4655888960075587</v>
+        <v>-0.4403257262108324</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3712936424368455</v>
+        <v>-0.3751076269319831</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05066734487869418</v>
+        <v>0.05530105610712956</v>
       </c>
       <c r="I36" t="n">
         <v>0.2400310166415557</v>
@@ -5711,28 +6912,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>49.02553888888889</v>
+        <v>51.95499999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>4.437096283654059</v>
+        <v>6.693003396669408</v>
       </c>
       <c r="E37" t="n">
         <v>43.83333333333334</v>
       </c>
       <c r="F37" t="n">
-        <v>46.35</v>
+        <v>46.75</v>
       </c>
       <c r="G37" t="n">
-        <v>47.05</v>
+        <v>50.21278333333333</v>
       </c>
       <c r="H37" t="n">
-        <v>52.5</v>
+        <v>56.56375416666666</v>
       </c>
       <c r="I37" t="n">
-        <v>56.05</v>
+        <v>63.03526666666667</v>
       </c>
     </row>
     <row r="38">
@@ -5742,13 +6943,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>31.4269</v>
+        <v>31.42711944444445</v>
       </c>
       <c r="D38" t="n">
-        <v>5.912487455095923</v>
+        <v>5.821956222617308</v>
       </c>
       <c r="E38" t="n">
         <v>25.12543333333333</v>
@@ -5773,28 +6974,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C39" t="n">
-        <v>17.59863888888889</v>
+        <v>20.52788055555556</v>
       </c>
       <c r="D39" t="n">
-        <v>7.534261935429818</v>
+        <v>9.042792935223886</v>
       </c>
       <c r="E39" t="n">
         <v>7.666666666666671</v>
       </c>
       <c r="F39" t="n">
-        <v>13.36666666666667</v>
+        <v>14.29487916666667</v>
       </c>
       <c r="G39" t="n">
-        <v>16.53333333333334</v>
+        <v>21.82061666666667</v>
       </c>
       <c r="H39" t="n">
-        <v>22.03333333333333</v>
+        <v>24.2537625</v>
       </c>
       <c r="I39" t="n">
-        <v>30.91666666666667</v>
+        <v>37.90193333333335</v>
       </c>
     </row>
     <row r="40">
@@ -5804,28 +7005,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>39.83041884252064</v>
+        <v>41.02298235166948</v>
       </c>
       <c r="D40" t="n">
-        <v>3.403197786155423</v>
+        <v>3.690357573661512</v>
       </c>
       <c r="E40" t="n">
-        <v>36.80847059423598</v>
+        <v>36.70010973267537</v>
       </c>
       <c r="F40" t="n">
-        <v>37.60735272104981</v>
+        <v>37.606340707808</v>
       </c>
       <c r="G40" t="n">
-        <v>38.07535235688084</v>
+        <v>40.94369908853516</v>
       </c>
       <c r="H40" t="n">
-        <v>43.39133179794914</v>
+        <v>44.47366833289454</v>
       </c>
       <c r="I40" t="n">
-        <v>44.91739841291827</v>
+        <v>45.7896379485424</v>
       </c>
     </row>
     <row r="41">
@@ -5835,22 +7036,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C41" t="n">
-        <v>21.72994439358199</v>
+        <v>21.73246776952415</v>
       </c>
       <c r="D41" t="n">
-        <v>5.010046551574879</v>
+        <v>4.933546834869</v>
       </c>
       <c r="E41" t="n">
         <v>16.04368253659841</v>
       </c>
       <c r="F41" t="n">
-        <v>16.04658812968748</v>
+        <v>16.04586173141521</v>
       </c>
       <c r="G41" t="n">
-        <v>21.52228685090974</v>
+        <v>21.54277919776302</v>
       </c>
       <c r="H41" t="n">
         <v>27.60990969505806</v>
@@ -5866,28 +7067,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C42" t="n">
-        <v>18.10047444893866</v>
+        <v>19.29051458214531</v>
       </c>
       <c r="D42" t="n">
-        <v>6.145412380708724</v>
+        <v>6.298571972161881</v>
       </c>
       <c r="E42" t="n">
-        <v>10.1043694704332</v>
+        <v>9.993394973024532</v>
       </c>
       <c r="F42" t="n">
-        <v>15.24781268546773</v>
+        <v>15.25036834870169</v>
       </c>
       <c r="G42" t="n">
-        <v>16.90252039329641</v>
+        <v>19.45005205139246</v>
       </c>
       <c r="H42" t="n">
-        <v>21.8690449470394</v>
+        <v>22.25202481469283</v>
       </c>
       <c r="I42" t="n">
-        <v>28.87371587631986</v>
+        <v>29.74595541194399</v>
       </c>
     </row>
     <row r="43">
@@ -5897,28 +7098,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>35.58091296296296</v>
+        <v>37.41874722222222</v>
       </c>
       <c r="D43" t="n">
-        <v>2.958741991865633</v>
+        <v>4.676515648557558</v>
       </c>
       <c r="E43" t="n">
-        <v>30.75</v>
+        <v>30.25</v>
       </c>
       <c r="F43" t="n">
-        <v>34.2</v>
+        <v>34.58750000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>35.55</v>
+        <v>36.62081666666666</v>
       </c>
       <c r="H43" t="n">
-        <v>37.57496666666667</v>
+        <v>40.375</v>
       </c>
       <c r="I43" t="n">
-        <v>40.11666666666667</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="44">
@@ -5928,13 +7129,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
-        <v>24.52222222222222</v>
+        <v>24.41666666666667</v>
       </c>
       <c r="D44" t="n">
-        <v>1.967302157213724</v>
+        <v>1.782122216897484</v>
       </c>
       <c r="E44" t="n">
         <v>23</v>
@@ -5946,10 +7147,10 @@
         <v>23.43333333333333</v>
       </c>
       <c r="H44" t="n">
-        <v>27.13333333333333</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="I44" t="n">
-        <v>27.13333333333333</v>
+        <v>26.81666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -5959,28 +7160,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C45" t="n">
-        <v>11.05869074074074</v>
+        <v>13.00208055555556</v>
       </c>
       <c r="D45" t="n">
-        <v>3.456576737068604</v>
+        <v>4.906758596500855</v>
       </c>
       <c r="E45" t="n">
-        <v>5.419916666666669</v>
+        <v>5.166666666666661</v>
       </c>
       <c r="F45" t="n">
-        <v>8.533333333333328</v>
+        <v>9.725000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>11.71666666666667</v>
+        <v>12.075</v>
       </c>
       <c r="H45" t="n">
-        <v>12.11666666666667</v>
+        <v>16.8125</v>
       </c>
       <c r="I45" t="n">
-        <v>16.68333333333334</v>
+        <v>22.01666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -5990,28 +7191,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C46" t="n">
-        <v>28.12192345936337</v>
+        <v>29.07212415296469</v>
       </c>
       <c r="D46" t="n">
-        <v>2.05115676610251</v>
+        <v>2.820642436973817</v>
       </c>
       <c r="E46" t="n">
-        <v>25.36797775428393</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="F46" t="n">
-        <v>26.86273516629103</v>
+        <v>27.04170208891873</v>
       </c>
       <c r="G46" t="n">
-        <v>27.61065850344794</v>
+        <v>29.01242314446199</v>
       </c>
       <c r="H46" t="n">
-        <v>30.28204152472709</v>
+        <v>31.10082900058318</v>
       </c>
       <c r="I46" t="n">
-        <v>31.03077014131876</v>
+        <v>33.36307095293761</v>
       </c>
     </row>
     <row r="47">
@@ -6021,13 +7222,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
-        <v>17.94877215980477</v>
+        <v>17.91146000917135</v>
       </c>
       <c r="D47" t="n">
-        <v>1.539500784586656</v>
+        <v>1.468392570201946</v>
       </c>
       <c r="E47" t="n">
         <v>16.77959665852362</v>
@@ -6036,13 +7237,13 @@
         <v>16.77959665852362</v>
       </c>
       <c r="G47" t="n">
-        <v>17.07262314327449</v>
+        <v>17.07123764974337</v>
       </c>
       <c r="H47" t="n">
-        <v>19.99447365781878</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="I47" t="n">
-        <v>19.99447365781878</v>
+        <v>19.89292827190748</v>
       </c>
     </row>
     <row r="48">
@@ -6052,28 +7253,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" t="n">
-        <v>10.1731512995586</v>
+        <v>11.16066414379333</v>
       </c>
       <c r="D48" t="n">
-        <v>2.540018679060849</v>
+        <v>3.158477689494613</v>
       </c>
       <c r="E48" t="n">
-        <v>6.217436836343481</v>
+        <v>5.830029835698312</v>
       </c>
       <c r="F48" t="n">
-        <v>8.298125598071682</v>
+        <v>9.092783881227627</v>
       </c>
       <c r="G48" t="n">
-        <v>10.2191119279191</v>
+        <v>10.8165856206056</v>
       </c>
       <c r="H48" t="n">
-        <v>10.83106184492432</v>
+        <v>13.46985715678824</v>
       </c>
       <c r="I48" t="n">
-        <v>14.25117348279514</v>
+        <v>16.58347429441399</v>
       </c>
     </row>
     <row r="49">
@@ -6083,28 +7284,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" t="n">
-        <v>101.6469388888889</v>
+        <v>88.59827777777777</v>
       </c>
       <c r="D49" t="n">
-        <v>6.66179949147773</v>
+        <v>10.67225357170662</v>
       </c>
       <c r="E49" t="n">
-        <v>87.70028333333333</v>
+        <v>69.61666666666666</v>
       </c>
       <c r="F49" t="n">
-        <v>98.77674999999999</v>
+        <v>81.09604583333333</v>
       </c>
       <c r="G49" t="n">
-        <v>103.7522</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>106.6166666666667</v>
+        <v>94.67500000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>109.1269666666667</v>
+        <v>102.3936333333333</v>
       </c>
     </row>
     <row r="50">
@@ -6114,28 +7315,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" t="n">
-        <v>136.4296296296296</v>
+        <v>131.9288874999999</v>
       </c>
       <c r="D50" t="n">
-        <v>14.57892737675819</v>
+        <v>11.77349010299878</v>
       </c>
       <c r="E50" t="n">
-        <v>120.7166666666667</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="F50" t="n">
-        <v>120.7166666666667</v>
+        <v>117.2308208333334</v>
       </c>
       <c r="G50" t="n">
         <v>134.3833333333333</v>
       </c>
       <c r="H50" t="n">
-        <v>153.4</v>
+        <v>143.7458333333333</v>
       </c>
       <c r="I50" t="n">
-        <v>154.5833333333333</v>
+        <v>144.6333333333333</v>
       </c>
     </row>
     <row r="51">
@@ -6145,28 +7346,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" t="n">
-        <v>-34.78269074074072</v>
+        <v>-43.3306097222222</v>
       </c>
       <c r="D51" t="n">
-        <v>13.86917263414445</v>
+        <v>15.52639965022991</v>
       </c>
       <c r="E51" t="n">
-        <v>-48.1032</v>
+        <v>-69.6333333333333</v>
       </c>
       <c r="F51" t="n">
-        <v>-46.68304999999997</v>
+        <v>-51.28742916666663</v>
       </c>
       <c r="G51" t="n">
-        <v>-37.40539999999996</v>
+        <v>-42.57144999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>-21.08333333333336</v>
+        <v>-37.45998750000002</v>
       </c>
       <c r="I51" t="n">
-        <v>-14.09999999999999</v>
+        <v>-18.48333333333331</v>
       </c>
     </row>
     <row r="52">
@@ -6176,28 +7377,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" t="n">
-        <v>76.68840892922483</v>
+        <v>73.55007302317372</v>
       </c>
       <c r="D52" t="n">
-        <v>5.740641327530124</v>
+        <v>6.106445159595658</v>
       </c>
       <c r="E52" t="n">
-        <v>67.23643719629696</v>
+        <v>65.77016461009407</v>
       </c>
       <c r="F52" t="n">
-        <v>71.26833841096357</v>
+        <v>67.72642658111778</v>
       </c>
       <c r="G52" t="n">
-        <v>78.83492659413233</v>
+        <v>73.78896644386801</v>
       </c>
       <c r="H52" t="n">
-        <v>81.17353080024326</v>
+        <v>79.50266411531703</v>
       </c>
       <c r="I52" t="n">
-        <v>82.21470927818682</v>
+        <v>81.51318776562465</v>
       </c>
     </row>
     <row r="53">
@@ -6207,28 +7408,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C53" t="n">
-        <v>104.5183923836226</v>
+        <v>103.7803480898824</v>
       </c>
       <c r="D53" t="n">
-        <v>7.389535114891602</v>
+        <v>6.640206831295481</v>
       </c>
       <c r="E53" t="n">
-        <v>97.0168296725888</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="F53" t="n">
-        <v>97.0168296725888</v>
+        <v>96.57289895821184</v>
       </c>
       <c r="G53" t="n">
         <v>102.738159054381</v>
       </c>
       <c r="H53" t="n">
-        <v>113.6030563965588</v>
+        <v>111.875881290185</v>
       </c>
       <c r="I53" t="n">
-        <v>113.9111543824703</v>
+        <v>112.1322772301322</v>
       </c>
     </row>
     <row r="54">
@@ -6238,28 +7439,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C54" t="n">
-        <v>-27.82998345439772</v>
+        <v>-30.23027506670869</v>
       </c>
       <c r="D54" t="n">
-        <v>8.605326039788832</v>
+        <v>8.48478324998926</v>
       </c>
       <c r="E54" t="n">
-        <v>-42.61801608170103</v>
+        <v>-44.15683988070923</v>
       </c>
       <c r="F54" t="n">
-        <v>-31.78922784452642</v>
+        <v>-36.1153066385055</v>
       </c>
       <c r="G54" t="n">
-        <v>-27.21537520569123</v>
+        <v>-29.94386800267227</v>
       </c>
       <c r="H54" t="n">
-        <v>-23.90323246024867</v>
+        <v>-25.87179405563644</v>
       </c>
       <c r="I54" t="n">
-        <v>-15.84329887234554</v>
+        <v>-16.97328821885483</v>
       </c>
     </row>
   </sheetData>
@@ -6277,32 +7478,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Pair_Count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Mean_EV_TAT_min</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_ICE_TAT_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_TAT_Difference_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Median_TAT_Difference_min</t>
         </is>
@@ -6315,19 +7516,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>212.3691203703704</v>
+        <v>219.6213375</v>
       </c>
       <c r="D2" t="n">
-        <v>254.4617018518519</v>
+        <v>254.273775</v>
       </c>
       <c r="E2" t="n">
-        <v>-42.09258148148149</v>
+        <v>-34.65243750000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-36.32509999999999</v>
+        <v>-34.47040833333335</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plot</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>16_clustered_phase_heatmap.png</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Constant phase dimensions omitted: charging_refueling_time_diff_min</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data/Results/Visualizations/INTERCITY/Route_Wise/Chennai_to_Pondicherry/Average/Master_Results.xlsx
+++ b/Data/Results/Visualizations/INTERCITY/Route_Wise/Chennai_to_Pondicherry/Average/Master_Results.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF13"/>
+  <dimension ref="A1:BF17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,34 +1685,34 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>247.26765</v>
+        <v>299.5047</v>
       </c>
       <c r="H7" t="n">
-        <v>274.35</v>
+        <v>285.5666666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>148.4081122812309</v>
+        <v>153.5348441515956</v>
       </c>
       <c r="J7" t="n">
-        <v>148.1693420519742</v>
+        <v>153.5526617847118</v>
       </c>
       <c r="K7" t="n">
-        <v>47.63775321159345</v>
+        <v>41.13690324412203</v>
       </c>
       <c r="L7" t="n">
-        <v>44.79805655414056</v>
+        <v>41.3531214666836</v>
       </c>
       <c r="M7" t="n">
-        <v>-27.08235000000002</v>
+        <v>13.93803333333329</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2387702292566871</v>
+        <v>-0.01781763311620921</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83969665745289</v>
+        <v>-0.2162182225615652</v>
       </c>
       <c r="P7" t="n">
-        <v>-17.70095000000001</v>
+        <v>11.25000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1733,126 +1733,126 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>35.56666666666667</v>
+        <v>68.95</v>
       </c>
       <c r="X7" t="n">
-        <v>69.48333333333333</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>-33.91666666666666</v>
+        <v>20.76666666666667</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5933262321891101</v>
+        <v>0.4749837040150751</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.8398781436089819</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.2465519114198719</v>
+        <v>-0.1777092768854175</v>
       </c>
       <c r="AC7" t="n">
-        <v>26.16571666666666</v>
+        <v>8.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>9.949999999999999</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="AE7" t="n">
-        <v>16.21571666666666</v>
+        <v>-9.516666666666671</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5067319571443681</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.797999630400208</v>
+        <v>1.46713538845297</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.29126767325584</v>
+        <v>-0.8912853565055244</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.05</v>
+        <v>8.016666666666667</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.716666666666667</v>
+        <v>9.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3333333333333328</v>
+        <v>-1.883333333333333</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1799078409944621</v>
+        <v>0.6265751975894123</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5759078527107181</v>
+        <v>1.3169091629821</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.396000011716256</v>
+        <v>-0.6903339653926877</v>
       </c>
       <c r="AO7" t="n">
-        <v>63.03526666666667</v>
+        <v>58.3</v>
       </c>
       <c r="AP7" t="n">
-        <v>25.13333333333333</v>
+        <v>51.03333333333333</v>
       </c>
       <c r="AQ7" t="n">
-        <v>37.90193333333335</v>
+        <v>7.266666666666666</v>
       </c>
       <c r="AR7" t="n">
-        <v>45.7896379485424</v>
+        <v>45.77282478240121</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.04368253659841</v>
+        <v>32.19133544608479</v>
       </c>
       <c r="AT7" t="n">
-        <v>29.74595541194399</v>
+        <v>13.58148933631642</v>
       </c>
       <c r="AU7" t="n">
-        <v>45.45</v>
+        <v>42.61666666666667</v>
       </c>
       <c r="AV7" t="n">
-        <v>23.43333333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AW7" t="n">
-        <v>22.01666666666667</v>
+        <v>5.483333333333334</v>
       </c>
       <c r="AX7" t="n">
-        <v>33.36307095293761</v>
+        <v>32.14941881546432</v>
       </c>
       <c r="AY7" t="n">
-        <v>16.77959665852362</v>
+        <v>24.26414905968165</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.58347429441399</v>
+        <v>7.885269755782673</v>
       </c>
       <c r="BA7" t="n">
-        <v>75</v>
+        <v>113.4713666666667</v>
       </c>
       <c r="BB7" t="n">
-        <v>144.6333333333333</v>
+        <v>121.65</v>
       </c>
       <c r="BC7" t="n">
-        <v>-69.6333333333333</v>
+        <v>-8.178633333333309</v>
       </c>
       <c r="BD7" t="n">
-        <v>67.97543734942298</v>
+        <v>73.93519162017814</v>
       </c>
       <c r="BE7" t="n">
-        <v>112.1322772301322</v>
+        <v>93.66043974660975</v>
       </c>
       <c r="BF7" t="n">
-        <v>-44.15683988070923</v>
+        <v>-19.72524812643161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1867,38 +1867,38 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_25-09-2026\PAIR_010_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>205.6434166666667</v>
+        <v>247.26765</v>
       </c>
       <c r="H8" t="n">
-        <v>221.15</v>
+        <v>274.35</v>
       </c>
       <c r="I8" t="n">
-        <v>141.5990549680233</v>
+        <v>148.4081122812309</v>
       </c>
       <c r="J8" t="n">
-        <v>141.6663057069586</v>
+        <v>148.1693420519742</v>
       </c>
       <c r="K8" t="n">
-        <v>51.08928882117495</v>
+        <v>47.63775321159345</v>
       </c>
       <c r="L8" t="n">
-        <v>44.82009341634151</v>
+        <v>44.79805655414056</v>
       </c>
       <c r="M8" t="n">
-        <v>-15.50658333333331</v>
+        <v>-27.08235000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0672507389353143</v>
+        <v>0.2387702292566871</v>
       </c>
       <c r="O8" t="n">
-        <v>6.26919540483344</v>
+        <v>2.83969665745289</v>
       </c>
       <c r="P8" t="n">
-        <v>10.43813333333333</v>
+        <v>-17.70095000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1919,126 +1919,126 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>30.18333333333333</v>
+        <v>35.56666666666667</v>
       </c>
       <c r="X8" t="n">
-        <v>31.8</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.616666666666671</v>
+        <v>-33.91666666666666</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3830658150971378</v>
+        <v>0.5933262321891101</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1615049145429354</v>
+        <v>-0.2465519114198719</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.0548</v>
+        <v>26.16571666666666</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE8" t="n">
-        <v>12.0548</v>
+        <v>16.21571666666666</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.078327234216284</v>
+        <v>0.5067319571443681</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.078327234216284</v>
+        <v>-1.29126767325584</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.5</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.3333333333333328</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.2046142102738726</v>
+        <v>0.1799078409944621</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0881394731161023</v>
+        <v>-0.396000011716256</v>
       </c>
       <c r="AO8" t="n">
-        <v>43.83333333333334</v>
+        <v>63.03526666666667</v>
       </c>
       <c r="AP8" t="n">
-        <v>30.46666666666667</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.36666666666667</v>
+        <v>37.90193333333335</v>
       </c>
       <c r="AR8" t="n">
-        <v>36.80847059423598</v>
+        <v>45.7896379485424</v>
       </c>
       <c r="AS8" t="n">
-        <v>21.52025885865341</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.28821173558257</v>
+        <v>29.74595541194399</v>
       </c>
       <c r="AU8" t="n">
-        <v>30.25</v>
+        <v>45.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.25</v>
+        <v>22.01666666666667</v>
       </c>
       <c r="AX8" t="n">
-        <v>24.89543913557874</v>
+        <v>33.36307095293761</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.06985215621225</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.825586979366491</v>
+        <v>16.58347429441399</v>
       </c>
       <c r="BA8" t="n">
-        <v>87.22195000000001</v>
+        <v>75</v>
       </c>
       <c r="BB8" t="n">
-        <v>134.3833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BC8" t="n">
-        <v>-47.16138333333329</v>
+        <v>-69.6333333333333</v>
       </c>
       <c r="BD8" t="n">
-        <v>77.22913797862124</v>
+        <v>67.97543734942298</v>
       </c>
       <c r="BE8" t="n">
-        <v>102.738159054381</v>
+        <v>112.1322772301322</v>
       </c>
       <c r="BF8" t="n">
-        <v>-25.50902107575976</v>
+        <v>-44.15683988070923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2053,38 +2053,38 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_018_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>219.9365833333333</v>
+        <v>205.6434166666667</v>
       </c>
       <c r="H9" t="n">
-        <v>269.2166666666666</v>
+        <v>221.15</v>
       </c>
       <c r="I9" t="n">
-        <v>146.1177802267258</v>
+        <v>141.5990549680233</v>
       </c>
       <c r="J9" t="n">
-        <v>146.2265476173816</v>
+        <v>141.6663057069586</v>
       </c>
       <c r="K9" t="n">
-        <v>48.97751792605069</v>
+        <v>51.08928882117495</v>
       </c>
       <c r="L9" t="n">
-        <v>44.8576416936978</v>
+        <v>44.82009341634151</v>
       </c>
       <c r="M9" t="n">
-        <v>-49.28008333333329</v>
+        <v>-15.50658333333331</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1087673906557995</v>
+        <v>-0.0672507389353143</v>
       </c>
       <c r="O9" t="n">
-        <v>4.119876232352887</v>
+        <v>6.26919540483344</v>
       </c>
       <c r="P9" t="n">
-        <v>-31.04675</v>
+        <v>10.43813333333333</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2108,119 +2108,119 @@
         <v>30.18333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>71.08333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>-40.9</v>
+        <v>-1.616666666666671</v>
       </c>
       <c r="Z9" t="n">
         <v>0.3830658150971378</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5719741256040581</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.1889083105069204</v>
+        <v>0.1615049145429354</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.90325</v>
+        <v>12.0548</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>9.853249999999999</v>
+        <v>12.0548</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.189772290028397</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.5525630686911562</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.637209221337241</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.233333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>-7.366666666666666</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.2739207603422623</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.033360466311896</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.7594397059696337</v>
+        <v>0.0881394731161023</v>
       </c>
       <c r="AO9" t="n">
-        <v>46.35</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="AP9" t="n">
-        <v>38.68333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.666666666666671</v>
+        <v>13.36666666666667</v>
       </c>
       <c r="AR9" t="n">
-        <v>38.07535235688084</v>
+        <v>36.80847059423598</v>
       </c>
       <c r="AS9" t="n">
-        <v>27.60990969505806</v>
+        <v>21.52025885865341</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.46544266182278</v>
+        <v>15.28821173558257</v>
       </c>
       <c r="AU9" t="n">
-        <v>31.98333333333333</v>
+        <v>30.25</v>
       </c>
       <c r="AV9" t="n">
-        <v>26.81666666666667</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.166666666666661</v>
+        <v>7.25</v>
       </c>
       <c r="AX9" t="n">
-        <v>25.72295810760579</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="AY9" t="n">
-        <v>19.89292827190748</v>
+        <v>17.06985215621225</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.830029835698312</v>
+        <v>7.825586979366491</v>
       </c>
       <c r="BA9" t="n">
-        <v>93.28333333333333</v>
+        <v>87.22195000000001</v>
       </c>
       <c r="BB9" t="n">
-        <v>116.9833333333333</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="BC9" t="n">
-        <v>-23.69999999999997</v>
+        <v>-47.16138333333329</v>
       </c>
       <c r="BD9" t="n">
-        <v>79.47271089677133</v>
+        <v>77.22913797862124</v>
       </c>
       <c r="BE9" t="n">
-        <v>96.56581198980894</v>
+        <v>102.738159054381</v>
       </c>
       <c r="BF9" t="n">
-        <v>-17.0931010930376</v>
+        <v>-25.50902107575976</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2239,38 +2239,38 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>186.11555</v>
+        <v>219.9365833333333</v>
       </c>
       <c r="H10" t="n">
-        <v>221.15</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="I10" t="n">
-        <v>141.7178099447946</v>
+        <v>146.1177802267258</v>
       </c>
       <c r="J10" t="n">
-        <v>141.7137294264382</v>
+        <v>146.2265476173816</v>
       </c>
       <c r="K10" t="n">
-        <v>48.97984764694002</v>
+        <v>48.97751792605069</v>
       </c>
       <c r="L10" t="n">
-        <v>44.83512073701105</v>
+        <v>44.8576416936978</v>
       </c>
       <c r="M10" t="n">
-        <v>-35.03444999999999</v>
+        <v>-49.28008333333329</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004080518356403218</v>
+        <v>-0.1087673906557995</v>
       </c>
       <c r="O10" t="n">
-        <v>4.14472690992897</v>
+        <v>4.119876232352887</v>
       </c>
       <c r="P10" t="n">
-        <v>-18.08873333333333</v>
+        <v>-31.04675</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2291,122 +2291,122 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X10" t="n">
-        <v>31.8</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>-22.86666666666667</v>
+        <v>-40.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.5719741256040581</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03761503109371811</v>
+        <v>-0.1889083105069204</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.777933333333333</v>
+        <v>13.90325</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>4.777933333333333</v>
+        <v>9.853249999999999</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.7197084907042335</v>
+        <v>2.189772290028397</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.7197084907042335</v>
+        <v>1.637209221337241</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.5</v>
+        <v>-7.366666666666666</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>0.2739207603422623</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.1164747371577703</v>
+        <v>1.033360466311896</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.1164747371577703</v>
+        <v>-0.7594397059696337</v>
       </c>
       <c r="AO10" t="n">
-        <v>45.07095</v>
+        <v>46.35</v>
       </c>
       <c r="AP10" t="n">
-        <v>30.46666666666667</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.60428333333333</v>
+        <v>7.666666666666671</v>
       </c>
       <c r="AR10" t="n">
-        <v>36.70010973267537</v>
+        <v>38.07535235688084</v>
       </c>
       <c r="AS10" t="n">
-        <v>21.5632715446163</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="AT10" t="n">
-        <v>15.13683818805907</v>
+        <v>10.46544266182278</v>
       </c>
       <c r="AU10" t="n">
-        <v>34.96666666666667</v>
+        <v>31.98333333333333</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AW10" t="n">
-        <v>11.96666666666667</v>
+        <v>5.166666666666661</v>
       </c>
       <c r="AX10" t="n">
-        <v>27.29337511764809</v>
+        <v>25.72295810760579</v>
       </c>
       <c r="AY10" t="n">
-        <v>17.07426318972899</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.2191119279191</v>
+        <v>5.830029835698312</v>
       </c>
       <c r="BA10" t="n">
-        <v>92.36666666666666</v>
+        <v>93.28333333333333</v>
       </c>
       <c r="BB10" t="n">
-        <v>134.3833333333333</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BC10" t="n">
-        <v>-42.01666666666664</v>
+        <v>-23.69999999999997</v>
       </c>
       <c r="BD10" t="n">
-        <v>76.745440672119</v>
+        <v>79.47271089677133</v>
       </c>
       <c r="BE10" t="n">
-        <v>102.738159054381</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BF10" t="n">
-        <v>-25.992718382262</v>
+        <v>-17.0931010930376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2425,38 +2425,38 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_020_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>221.1224333333333</v>
+        <v>186.11555</v>
       </c>
       <c r="H11" t="n">
         <v>221.15</v>
       </c>
       <c r="I11" t="n">
-        <v>141.8317368861638</v>
+        <v>141.7178099447946</v>
       </c>
       <c r="J11" t="n">
-        <v>141.6733980516045</v>
+        <v>141.7137294264382</v>
       </c>
       <c r="K11" t="n">
-        <v>49.27030586470386</v>
+        <v>48.97984764694002</v>
       </c>
       <c r="L11" t="n">
-        <v>44.82234079251659</v>
+        <v>44.83512073701105</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02756666666670071</v>
+        <v>-35.03444999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1583388345593164</v>
+        <v>0.004080518356403218</v>
       </c>
       <c r="O11" t="n">
-        <v>4.447965072187266</v>
+        <v>4.14472690992897</v>
       </c>
       <c r="P11" t="n">
-        <v>17.65075</v>
+        <v>-18.08873333333333</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2477,126 +2477,126 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>30.46666666666667</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="X11" t="n">
         <v>31.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.333333333333332</v>
+        <v>-22.86666666666667</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4844248901091631</v>
+        <v>0.2591759316479205</v>
       </c>
       <c r="AA11" t="n">
         <v>0.2215609005542024</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.2628639895549607</v>
+        <v>0.03761503109371811</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.98408333333333</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.98408333333333</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.3753728936893338</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.3753728936893338</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.7999999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.185676926950206</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
         <v>0.1164747371577703</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.06920218979243568</v>
+        <v>-0.1164747371577703</v>
       </c>
       <c r="AO11" t="n">
-        <v>58.60501666666666</v>
+        <v>45.07095</v>
       </c>
       <c r="AP11" t="n">
         <v>30.46666666666667</v>
       </c>
       <c r="AQ11" t="n">
-        <v>28.13834999999999</v>
+        <v>14.60428333333333</v>
       </c>
       <c r="AR11" t="n">
-        <v>43.70509198694462</v>
+        <v>36.70010973267537</v>
       </c>
       <c r="AS11" t="n">
-        <v>21.5665214603954</v>
+        <v>21.5632715446163</v>
       </c>
       <c r="AT11" t="n">
-        <v>22.13857052654922</v>
+        <v>15.13683818805907</v>
       </c>
       <c r="AU11" t="n">
-        <v>41.15</v>
+        <v>34.96666666666667</v>
       </c>
       <c r="AV11" t="n">
         <v>23</v>
       </c>
       <c r="AW11" t="n">
-        <v>18.15</v>
+        <v>11.96666666666667</v>
       </c>
       <c r="AX11" t="n">
-        <v>31.31100557837641</v>
+        <v>27.29337511764809</v>
       </c>
       <c r="AY11" t="n">
-        <v>17.03068189911616</v>
+        <v>17.07426318972899</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.28032367926025</v>
+        <v>10.2191119279191</v>
       </c>
       <c r="BA11" t="n">
-        <v>69.61666666666666</v>
+        <v>92.36666666666666</v>
       </c>
       <c r="BB11" t="n">
         <v>134.3833333333333</v>
       </c>
       <c r="BC11" t="n">
-        <v>-64.76666666666664</v>
+        <v>-42.01666666666664</v>
       </c>
       <c r="BD11" t="n">
-        <v>65.77016461009407</v>
+        <v>76.745440672119</v>
       </c>
       <c r="BE11" t="n">
         <v>102.738159054381</v>
       </c>
       <c r="BF11" t="n">
-        <v>-36.96799444428693</v>
+        <v>-25.992718382262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2611,38 +2611,38 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_021_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>195.4022</v>
+        <v>235.7315</v>
       </c>
       <c r="H12" t="n">
-        <v>266.8632166666667</v>
+        <v>285.5666666666667</v>
       </c>
       <c r="I12" t="n">
-        <v>145.9064422742808</v>
+        <v>153.5802936448807</v>
       </c>
       <c r="J12" t="n">
-        <v>145.9943306994593</v>
+        <v>153.5880362119665</v>
       </c>
       <c r="K12" t="n">
-        <v>48.03268705989514</v>
+        <v>47.72215002408557</v>
       </c>
       <c r="L12" t="n">
-        <v>45.34276468747346</v>
+        <v>41.36278147867761</v>
       </c>
       <c r="M12" t="n">
-        <v>-71.46101666666669</v>
+        <v>-49.83516666666671</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.08788842517850526</v>
+        <v>-0.007742567085813334</v>
       </c>
       <c r="O12" t="n">
-        <v>2.689922372421677</v>
+        <v>6.35936854540796</v>
       </c>
       <c r="P12" t="n">
-        <v>-60.78113333333333</v>
+        <v>-19.73333333333333</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2663,122 +2663,122 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="X12" t="n">
-        <v>71.08333333333333</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="Y12" t="n">
-        <v>-62.14999999999999</v>
+        <v>-18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5490512384335874</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2898753067856669</v>
+        <v>-0.2696271658033549</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.418866666666667</v>
+        <v>15.93333333333333</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.05</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.368866666666667</v>
+        <v>-1.733333333333341</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.7086331393992357</v>
+        <v>2.383435777694972</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.5525630686911562</v>
+        <v>1.46713538845297</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1560700707080794</v>
+        <v>0.9163003892420019</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.246550000000001</v>
+        <v>9.9</v>
       </c>
       <c r="AK12" t="n">
-        <v>-9.246550000000001</v>
+        <v>-7.800000000000001</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.8240664355600736</v>
+        <v>1.3169091629821</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.8240664355600736</v>
+        <v>-1.112294952708227</v>
       </c>
       <c r="AO12" t="n">
-        <v>46.88333333333333</v>
+        <v>50.65</v>
       </c>
       <c r="AP12" t="n">
-        <v>38.68333333333333</v>
+        <v>51.03333333333333</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.200000000000003</v>
+        <v>-0.3833333333333329</v>
       </c>
       <c r="AR12" t="n">
-        <v>37.60330466808259</v>
+        <v>40.28614742330923</v>
       </c>
       <c r="AS12" t="n">
-        <v>27.60990969505806</v>
+        <v>32.22664079654989</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.993394973024532</v>
+        <v>8.059506626759344</v>
       </c>
       <c r="AU12" t="n">
-        <v>35.66666666666666</v>
+        <v>37.05954999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>26.81666666666667</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.849999999999987</v>
+        <v>-0.07378333333334552</v>
       </c>
       <c r="AX12" t="n">
-        <v>27.74280476419689</v>
+        <v>27.90182873497321</v>
       </c>
       <c r="AY12" t="n">
-        <v>19.89292827190748</v>
+        <v>24.26414905968165</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7.849876492289411</v>
+        <v>3.637679675291562</v>
       </c>
       <c r="BA12" t="n">
-        <v>98.5</v>
+        <v>99.80528333333334</v>
       </c>
       <c r="BB12" t="n">
-        <v>116.9833333333333</v>
+        <v>121.65</v>
       </c>
       <c r="BC12" t="n">
-        <v>-18.48333333333331</v>
+        <v>-21.84471666666667</v>
       </c>
       <c r="BD12" t="n">
-        <v>79.5925237709541</v>
+        <v>82.42120168353226</v>
       </c>
       <c r="BE12" t="n">
-        <v>96.56581198980894</v>
+        <v>93.6605088233994</v>
       </c>
       <c r="BF12" t="n">
-        <v>-16.97328821885483</v>
+        <v>-11.23930713986714</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2797,164 +2797,908 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_022_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>221.1224333333333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>141.8317368861638</v>
+      </c>
+      <c r="J13" t="n">
+        <v>141.6733980516045</v>
+      </c>
+      <c r="K13" t="n">
+        <v>49.27030586470386</v>
+      </c>
+      <c r="L13" t="n">
+        <v>44.82234079251659</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.02756666666670071</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1583388345593164</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.447965072187266</v>
+      </c>
+      <c r="P13" t="n">
+        <v>17.65075</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="X13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1.333333333333332</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4844248901091631</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.2215609005542024</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.2628639895549607</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>18.98408333333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.3753728936893338</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.185676926950206</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1164747371577703</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.06920218979243568</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>58.60501666666666</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>30.46666666666667</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>28.13834999999999</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>43.70509198694462</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>21.5665214603954</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>22.13857052654922</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>31.31100557837641</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17.03068189911616</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.28032367926025</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>69.61666666666666</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-64.76666666666664</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>65.77016461009407</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-36.96799444428693</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>28</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_028_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>195.4022</v>
+      </c>
+      <c r="H14" t="n">
+        <v>266.8632166666667</v>
+      </c>
+      <c r="I14" t="n">
+        <v>145.9064422742808</v>
+      </c>
+      <c r="J14" t="n">
+        <v>145.9943306994593</v>
+      </c>
+      <c r="K14" t="n">
+        <v>48.03268705989514</v>
+      </c>
+      <c r="L14" t="n">
+        <v>45.34276468747346</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-71.46101666666669</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.08788842517850526</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.689922372421677</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-60.78113333333333</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8.933333333333334</v>
+      </c>
+      <c r="X14" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-62.14999999999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.2591759316479205</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5490512384335874</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.2898753067856669</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.418866666666667</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.368866666666667</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.7086331393992357</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.1560700707080794</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>9.246550000000001</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-9.246550000000001</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.8240664355600736</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.8240664355600736</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>46.88333333333333</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>37.60330466808259</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.993394973024532</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>35.66666666666666</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8.849999999999987</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>27.74280476419689</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.849876492289411</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>116.9833333333333</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-18.48333333333331</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>79.5925237709541</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>96.56581198980894</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-16.97328821885483</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>29</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_029_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>202.4542833333333</v>
+      </c>
+      <c r="H15" t="n">
+        <v>266.7375833333334</v>
+      </c>
+      <c r="I15" t="n">
+        <v>148.6184563331109</v>
+      </c>
+      <c r="J15" t="n">
+        <v>148.5522231625584</v>
+      </c>
+      <c r="K15" t="n">
+        <v>47.68589618099658</v>
+      </c>
+      <c r="L15" t="n">
+        <v>42.94452978486028</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-64.28330000000011</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.06623317055252187</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.7413663961363</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-44.90000000000001</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>12.03333333333333</v>
+      </c>
+      <c r="X15" t="n">
+        <v>48.18333333333333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-36.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.3736603870816042</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.6526929809004927</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.2790325938188885</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.916666666666667</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-8.750000000000004</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.8124960099708274</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.252848098218356</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.4403520882475287</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.149895932972568</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1.149895932972568</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>47.07095</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>47.50425</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.4332999999999956</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>37.76245819389838</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>30.80621122533811</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.956246968560272</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>35.88333333333333</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>34.78333333333333</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>27.85743429121439</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>23.37216669639708</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.485267594817309</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>81.8124074509457</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>91.31840822873183</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-9.506000777786127</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_030_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>255.7438833333333</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H16" t="n">
         <v>265.6299833333333</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I16" t="n">
         <v>145.9773325040056</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J16" t="n">
         <v>145.8893363990339</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K16" t="n">
         <v>47.2452299004206</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L16" t="n">
         <v>45.59497163487288</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M16" t="n">
         <v>-9.886100000000027</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N16" t="n">
         <v>0.08799610497169397</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O16" t="n">
         <v>1.65025826554772</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P16" t="n">
         <v>-3.295983333333339</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>45.16666666666666</v>
       </c>
-      <c r="X13" t="n">
+      <c r="X16" t="n">
         <v>71.08333333333333</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y16" t="n">
         <v>-25.91666666666667</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z16" t="n">
         <v>0.6992727007011277</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA16" t="n">
         <v>0.5752841088710083</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AB16" t="n">
         <v>0.1239885918301193</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC16" t="n">
         <v>26.67068333333333</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD16" t="n">
         <v>4.05</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE16" t="n">
         <v>22.62068333333333</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AF16" t="n">
         <v>0.4662856779261432</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AG16" t="n">
         <v>0.5525630686911562</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AH16" t="n">
         <v>-0.08627739076501301</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AI16" t="n">
         <v>2.883333333333333</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AJ16" t="n">
         <v>7.683333333333334</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK16" t="n">
         <v>-4.800000000000001</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AL16" t="n">
         <v>0.2514853038814903</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AM16" t="n">
         <v>0.6833899734934139</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN16" t="n">
         <v>-0.4319046696119236</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AO16" t="n">
         <v>61.42319999999999</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AP16" t="n">
         <v>38.68333333333333</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AQ16" t="n">
         <v>22.73986666666666</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AR16" t="n">
         <v>44.94924920648065</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AS16" t="n">
         <v>27.60990969505806</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AT16" t="n">
         <v>17.33933951142259</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AU16" t="n">
         <v>44.01666666666667</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AV16" t="n">
         <v>26.81666666666667</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AW16" t="n">
         <v>17.2</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AX16" t="n">
         <v>32.63164533881391</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AY16" t="n">
         <v>19.89292827190748</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AZ16" t="n">
         <v>12.73871706690643</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BA16" t="n">
         <v>75.58333333333333</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB16" t="n">
         <v>117.3133166666667</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BC16" t="n">
         <v>-41.72998333333337</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BD16" t="n">
         <v>66.97939427620221</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BE16" t="n">
         <v>96.5752612810128</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BF16" t="n">
         <v>-29.59586700481059</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>51</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\25-09-2026\PAIR_051_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>265.8149333333333</v>
+      </c>
+      <c r="H17" t="n">
+        <v>285.5666666666667</v>
+      </c>
+      <c r="I17" t="n">
+        <v>153.6764767050815</v>
+      </c>
+      <c r="J17" t="n">
+        <v>153.5307402784298</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45.91137366592437</v>
+      </c>
+      <c r="L17" t="n">
+        <v>41.34713516442955</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-19.75173333333345</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1457364266517231</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.56423850149482</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7007499999999993</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>35.56666666666667</v>
+      </c>
+      <c r="X17" t="n">
+        <v>48.18333333333333</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-12.61666666666666</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.5933262321891101</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.6526929809004927</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.05936674871138259</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>30.98408333333333</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>17.66666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>13.31741666666666</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.608277485360332</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.46713538845297</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.8588579030926381</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10.23333333333333</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-6.933333333333331</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.3072360563497603</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.325529204266642</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1.018293147916882</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>67.48085</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>51.03333333333333</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>16.44751666666667</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>47.84822798746782</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>32.19479692464096</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>15.65343106282686</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>48.56666666666667</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>37.13333333333333</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>11.43333333333334</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>34.79805765976413</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>24.26414905968165</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>10.53390860008248</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>79.91666666666667</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>121.3166666666667</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-41.40000000000003</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>69.52135128395038</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>93.62643672048709</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-24.10508543653671</v>
       </c>
     </row>
   </sheetData>
@@ -2968,7 +3712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4105,22 +4849,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35.56666666666667</v>
+        <v>68.95</v>
       </c>
       <c r="D38" t="n">
-        <v>69.48333333333333</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="E38" t="n">
-        <v>-33.91666666666666</v>
+        <v>20.76666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5933262321891101</v>
+        <v>0.4749837040150751</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8398781436089819</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2465519114198719</v>
+        <v>-0.1777092768854175</v>
       </c>
     </row>
     <row r="39">
@@ -4135,22 +4879,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26.16571666666666</v>
+        <v>8.15</v>
       </c>
       <c r="D39" t="n">
-        <v>9.949999999999999</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="E39" t="n">
-        <v>16.21571666666666</v>
+        <v>-9.516666666666671</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5067319571443681</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="G39" t="n">
-        <v>1.797999630400208</v>
+        <v>1.46713538845297</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.29126767325584</v>
+        <v>-0.8912853565055244</v>
       </c>
     </row>
     <row r="40">
@@ -4165,22 +4909,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.05</v>
+        <v>8.016666666666667</v>
       </c>
       <c r="D40" t="n">
-        <v>1.716666666666667</v>
+        <v>9.9</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3333333333333328</v>
+        <v>-1.883333333333333</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1799078409944621</v>
+        <v>0.6265751975894123</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5759078527107181</v>
+        <v>1.3169091629821</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.396000011716256</v>
+        <v>-0.6903339653926877</v>
       </c>
     </row>
     <row r="41">
@@ -4195,22 +4939,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>63.03526666666667</v>
+        <v>58.3</v>
       </c>
       <c r="D41" t="n">
-        <v>25.13333333333333</v>
+        <v>51.03333333333333</v>
       </c>
       <c r="E41" t="n">
-        <v>37.90193333333335</v>
+        <v>7.266666666666666</v>
       </c>
       <c r="F41" t="n">
-        <v>45.7896379485424</v>
+        <v>45.77282478240121</v>
       </c>
       <c r="G41" t="n">
-        <v>16.04368253659841</v>
+        <v>32.19133544608479</v>
       </c>
       <c r="H41" t="n">
-        <v>29.74595541194399</v>
+        <v>13.58148933631642</v>
       </c>
     </row>
     <row r="42">
@@ -4225,22 +4969,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>45.45</v>
+        <v>42.61666666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>23.43333333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="E42" t="n">
-        <v>22.01666666666667</v>
+        <v>5.483333333333334</v>
       </c>
       <c r="F42" t="n">
-        <v>33.36307095293761</v>
+        <v>32.14941881546432</v>
       </c>
       <c r="G42" t="n">
-        <v>16.77959665852362</v>
+        <v>24.26414905968165</v>
       </c>
       <c r="H42" t="n">
-        <v>16.58347429441399</v>
+        <v>7.885269755782673</v>
       </c>
     </row>
     <row r="43">
@@ -4255,28 +4999,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>75</v>
+        <v>113.4713666666667</v>
       </c>
       <c r="D43" t="n">
-        <v>144.6333333333333</v>
+        <v>121.65</v>
       </c>
       <c r="E43" t="n">
-        <v>-69.6333333333333</v>
+        <v>-8.178633333333309</v>
       </c>
       <c r="F43" t="n">
-        <v>67.97543734942298</v>
+        <v>73.93519162017814</v>
       </c>
       <c r="G43" t="n">
-        <v>112.1322772301322</v>
+        <v>93.66043974660975</v>
       </c>
       <c r="H43" t="n">
-        <v>-44.15683988070923</v>
+        <v>-19.72524812643161</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4306,7 +5050,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4315,28 +5059,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30.18333333333333</v>
+        <v>35.56666666666667</v>
       </c>
       <c r="D45" t="n">
-        <v>31.8</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.616666666666671</v>
+        <v>-33.91666666666666</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3830658150971378</v>
+        <v>0.5933262321891101</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1615049145429354</v>
+        <v>-0.2465519114198719</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4345,28 +5089,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>12.0548</v>
+        <v>26.16571666666666</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>12.0548</v>
+        <v>16.21571666666666</v>
       </c>
       <c r="F46" t="n">
-        <v>2.078327234216284</v>
+        <v>0.5067319571443681</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="H46" t="n">
-        <v>2.078327234216284</v>
+        <v>-1.29126767325584</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4375,28 +5119,28 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="D47" t="n">
-        <v>1.5</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.3333333333333328</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2046142102738726</v>
+        <v>0.1799078409944621</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.5759078527107181</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0881394731161023</v>
+        <v>-0.396000011716256</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4405,28 +5149,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>43.83333333333334</v>
+        <v>63.03526666666667</v>
       </c>
       <c r="D48" t="n">
-        <v>30.46666666666667</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="E48" t="n">
-        <v>13.36666666666667</v>
+        <v>37.90193333333335</v>
       </c>
       <c r="F48" t="n">
-        <v>36.80847059423598</v>
+        <v>45.7896379485424</v>
       </c>
       <c r="G48" t="n">
-        <v>21.52025885865341</v>
+        <v>16.04368253659841</v>
       </c>
       <c r="H48" t="n">
-        <v>15.28821173558257</v>
+        <v>29.74595541194399</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4435,28 +5179,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>30.25</v>
+        <v>45.45</v>
       </c>
       <c r="D49" t="n">
-        <v>23</v>
+        <v>23.43333333333333</v>
       </c>
       <c r="E49" t="n">
-        <v>7.25</v>
+        <v>22.01666666666667</v>
       </c>
       <c r="F49" t="n">
-        <v>24.89543913557874</v>
+        <v>33.36307095293761</v>
       </c>
       <c r="G49" t="n">
-        <v>17.06985215621225</v>
+        <v>16.77959665852362</v>
       </c>
       <c r="H49" t="n">
-        <v>7.825586979366491</v>
+        <v>16.58347429441399</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4465,28 +5209,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>87.22195000000001</v>
+        <v>75</v>
       </c>
       <c r="D50" t="n">
-        <v>134.3833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="E50" t="n">
-        <v>-47.16138333333329</v>
+        <v>-69.6333333333333</v>
       </c>
       <c r="F50" t="n">
-        <v>77.22913797862124</v>
+        <v>67.97543734942298</v>
       </c>
       <c r="G50" t="n">
-        <v>102.738159054381</v>
+        <v>112.1322772301322</v>
       </c>
       <c r="H50" t="n">
-        <v>-25.50902107575976</v>
+        <v>-44.15683988070923</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4516,7 +5260,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4528,25 +5272,25 @@
         <v>30.18333333333333</v>
       </c>
       <c r="D52" t="n">
-        <v>71.08333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="E52" t="n">
-        <v>-40.9</v>
+        <v>-1.616666666666671</v>
       </c>
       <c r="F52" t="n">
         <v>0.3830658150971378</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5719741256040581</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1889083105069204</v>
+        <v>0.1615049145429354</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4555,28 +5299,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>13.90325</v>
+        <v>12.0548</v>
       </c>
       <c r="D53" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>9.853249999999999</v>
+        <v>12.0548</v>
       </c>
       <c r="F53" t="n">
-        <v>2.189772290028397</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5525630686911562</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.637209221337241</v>
+        <v>2.078327234216284</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4585,28 +5329,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.233333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="D54" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="E54" t="n">
-        <v>-7.366666666666666</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2739207603422623</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="G54" t="n">
-        <v>1.033360466311896</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.7594397059696337</v>
+        <v>0.0881394731161023</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4615,28 +5359,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>46.35</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="D55" t="n">
-        <v>38.68333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="E55" t="n">
-        <v>7.666666666666671</v>
+        <v>13.36666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>38.07535235688084</v>
+        <v>36.80847059423598</v>
       </c>
       <c r="G55" t="n">
-        <v>27.60990969505806</v>
+        <v>21.52025885865341</v>
       </c>
       <c r="H55" t="n">
-        <v>10.46544266182278</v>
+        <v>15.28821173558257</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4645,28 +5389,28 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>31.98333333333333</v>
+        <v>30.25</v>
       </c>
       <c r="D56" t="n">
-        <v>26.81666666666667</v>
+        <v>23</v>
       </c>
       <c r="E56" t="n">
-        <v>5.166666666666661</v>
+        <v>7.25</v>
       </c>
       <c r="F56" t="n">
-        <v>25.72295810760579</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="G56" t="n">
-        <v>19.89292827190748</v>
+        <v>17.06985215621225</v>
       </c>
       <c r="H56" t="n">
-        <v>5.830029835698312</v>
+        <v>7.825586979366491</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4675,28 +5419,28 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>93.28333333333333</v>
+        <v>87.22195000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>116.9833333333333</v>
+        <v>134.3833333333333</v>
       </c>
       <c r="E57" t="n">
-        <v>-23.69999999999997</v>
+        <v>-47.16138333333329</v>
       </c>
       <c r="F57" t="n">
-        <v>79.47271089677133</v>
+        <v>77.22913797862124</v>
       </c>
       <c r="G57" t="n">
-        <v>96.56581198980894</v>
+        <v>102.738159054381</v>
       </c>
       <c r="H57" t="n">
-        <v>-17.0931010930376</v>
+        <v>-25.50902107575976</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4726,7 +5470,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4735,28 +5479,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="D59" t="n">
-        <v>31.8</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="E59" t="n">
-        <v>-22.86666666666667</v>
+        <v>-40.9</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.5719741256040581</v>
       </c>
       <c r="H59" t="n">
-        <v>0.03761503109371811</v>
+        <v>-0.1889083105069204</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4765,28 +5509,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4.777933333333333</v>
+        <v>13.90325</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="E60" t="n">
-        <v>4.777933333333333</v>
+        <v>9.853249999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7197084907042335</v>
+        <v>2.189772290028397</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7197084907042335</v>
+        <v>1.637209221337241</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4795,28 +5539,28 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>1.5</v>
+        <v>11.6</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.5</v>
+        <v>-7.366666666666666</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>0.2739207603422623</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1164747371577703</v>
+        <v>1.033360466311896</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1164747371577703</v>
+        <v>-0.7594397059696337</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4825,28 +5569,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>45.07095</v>
+        <v>46.35</v>
       </c>
       <c r="D62" t="n">
-        <v>30.46666666666667</v>
+        <v>38.68333333333333</v>
       </c>
       <c r="E62" t="n">
-        <v>14.60428333333333</v>
+        <v>7.666666666666671</v>
       </c>
       <c r="F62" t="n">
-        <v>36.70010973267537</v>
+        <v>38.07535235688084</v>
       </c>
       <c r="G62" t="n">
-        <v>21.5632715446163</v>
+        <v>27.60990969505806</v>
       </c>
       <c r="H62" t="n">
-        <v>15.13683818805907</v>
+        <v>10.46544266182278</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4855,28 +5599,28 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>34.96666666666667</v>
+        <v>31.98333333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>23</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="E63" t="n">
-        <v>11.96666666666667</v>
+        <v>5.166666666666661</v>
       </c>
       <c r="F63" t="n">
-        <v>27.29337511764809</v>
+        <v>25.72295810760579</v>
       </c>
       <c r="G63" t="n">
-        <v>17.07426318972899</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="H63" t="n">
-        <v>10.2191119279191</v>
+        <v>5.830029835698312</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_019</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4885,28 +5629,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>92.36666666666666</v>
+        <v>93.28333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>134.3833333333333</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="E64" t="n">
-        <v>-42.01666666666664</v>
+        <v>-23.69999999999997</v>
       </c>
       <c r="F64" t="n">
-        <v>76.745440672119</v>
+        <v>79.47271089677133</v>
       </c>
       <c r="G64" t="n">
-        <v>102.738159054381</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="H64" t="n">
-        <v>-25.992718382262</v>
+        <v>-17.0931010930376</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4936,7 +5680,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4945,28 +5689,28 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>30.46666666666667</v>
+        <v>8.933333333333334</v>
       </c>
       <c r="D66" t="n">
         <v>31.8</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.333333333333332</v>
+        <v>-22.86666666666667</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4844248901091631</v>
+        <v>0.2591759316479205</v>
       </c>
       <c r="G66" t="n">
         <v>0.2215609005542024</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2628639895549607</v>
+        <v>0.03761503109371811</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4975,28 +5719,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>18.98408333333333</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>18.98408333333333</v>
+        <v>4.777933333333333</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3753728936893338</v>
+        <v>0.7197084907042335</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3753728936893338</v>
+        <v>0.7197084907042335</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5005,28 +5749,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>1.5</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7999999999999998</v>
+        <v>-1.5</v>
       </c>
       <c r="F68" t="n">
-        <v>0.185676926950206</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0.1164747371577703</v>
       </c>
       <c r="H68" t="n">
-        <v>0.06920218979243568</v>
+        <v>-0.1164747371577703</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5035,28 +5779,28 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>58.60501666666666</v>
+        <v>45.07095</v>
       </c>
       <c r="D69" t="n">
         <v>30.46666666666667</v>
       </c>
       <c r="E69" t="n">
-        <v>28.13834999999999</v>
+        <v>14.60428333333333</v>
       </c>
       <c r="F69" t="n">
-        <v>43.70509198694462</v>
+        <v>36.70010973267537</v>
       </c>
       <c r="G69" t="n">
-        <v>21.5665214603954</v>
+        <v>21.5632715446163</v>
       </c>
       <c r="H69" t="n">
-        <v>22.13857052654922</v>
+        <v>15.13683818805907</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5065,28 +5809,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>41.15</v>
+        <v>34.96666666666667</v>
       </c>
       <c r="D70" t="n">
         <v>23</v>
       </c>
       <c r="E70" t="n">
-        <v>18.15</v>
+        <v>11.96666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>31.31100557837641</v>
+        <v>27.29337511764809</v>
       </c>
       <c r="G70" t="n">
-        <v>17.03068189911616</v>
+        <v>17.07426318972899</v>
       </c>
       <c r="H70" t="n">
-        <v>14.28032367926025</v>
+        <v>10.2191119279191</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PAIR_019</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5095,28 +5839,28 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>69.61666666666666</v>
+        <v>92.36666666666666</v>
       </c>
       <c r="D71" t="n">
         <v>134.3833333333333</v>
       </c>
       <c r="E71" t="n">
-        <v>-64.76666666666664</v>
+        <v>-42.01666666666664</v>
       </c>
       <c r="F71" t="n">
-        <v>65.77016461009407</v>
+        <v>76.745440672119</v>
       </c>
       <c r="G71" t="n">
         <v>102.738159054381</v>
       </c>
       <c r="H71" t="n">
-        <v>-36.96799444428693</v>
+        <v>-25.992718382262</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5146,7 +5890,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5155,28 +5899,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8.933333333333334</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="D73" t="n">
-        <v>71.08333333333333</v>
+        <v>48.18333333333333</v>
       </c>
       <c r="E73" t="n">
-        <v>-62.14999999999999</v>
+        <v>-18</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2591759316479205</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5490512384335874</v>
+        <v>0.6526929809004927</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.2898753067856669</v>
+        <v>-0.2696271658033549</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5185,28 +5929,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5.418866666666667</v>
+        <v>15.93333333333333</v>
       </c>
       <c r="D74" t="n">
-        <v>4.05</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="E74" t="n">
-        <v>1.368866666666667</v>
+        <v>-1.733333333333341</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7086331393992357</v>
+        <v>2.383435777694972</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5525630686911562</v>
+        <v>1.46713538845297</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1560700707080794</v>
+        <v>0.9163003892420019</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5215,28 +5959,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="D75" t="n">
-        <v>9.246550000000001</v>
+        <v>9.9</v>
       </c>
       <c r="E75" t="n">
-        <v>-9.246550000000001</v>
+        <v>-7.800000000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>0.2046142102738726</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8240664355600736</v>
+        <v>1.3169091629821</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.8240664355600736</v>
+        <v>-1.112294952708227</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5245,28 +5989,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>46.88333333333333</v>
+        <v>50.65</v>
       </c>
       <c r="D76" t="n">
-        <v>38.68333333333333</v>
+        <v>51.03333333333333</v>
       </c>
       <c r="E76" t="n">
-        <v>8.200000000000003</v>
+        <v>-0.3833333333333329</v>
       </c>
       <c r="F76" t="n">
-        <v>37.60330466808259</v>
+        <v>40.28614742330923</v>
       </c>
       <c r="G76" t="n">
-        <v>27.60990969505806</v>
+        <v>32.22664079654989</v>
       </c>
       <c r="H76" t="n">
-        <v>9.993394973024532</v>
+        <v>8.059506626759344</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5275,28 +6019,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>35.66666666666666</v>
+        <v>37.05954999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>26.81666666666667</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="E77" t="n">
-        <v>8.849999999999987</v>
+        <v>-0.07378333333334552</v>
       </c>
       <c r="F77" t="n">
-        <v>27.74280476419689</v>
+        <v>27.90182873497321</v>
       </c>
       <c r="G77" t="n">
-        <v>19.89292827190748</v>
+        <v>24.26414905968165</v>
       </c>
       <c r="H77" t="n">
-        <v>7.849876492289411</v>
+        <v>3.637679675291562</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5305,28 +6049,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>98.5</v>
+        <v>99.80528333333334</v>
       </c>
       <c r="D78" t="n">
-        <v>116.9833333333333</v>
+        <v>121.65</v>
       </c>
       <c r="E78" t="n">
-        <v>-18.48333333333331</v>
+        <v>-21.84471666666667</v>
       </c>
       <c r="F78" t="n">
-        <v>79.5925237709541</v>
+        <v>82.42120168353226</v>
       </c>
       <c r="G78" t="n">
-        <v>96.56581198980894</v>
+        <v>93.6605088233994</v>
       </c>
       <c r="H78" t="n">
-        <v>-16.97328821885483</v>
+        <v>-11.23930713986714</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5356,7 +6100,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5365,28 +6109,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>45.16666666666666</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="D80" t="n">
-        <v>71.08333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="E80" t="n">
-        <v>-25.91666666666667</v>
+        <v>-1.333333333333332</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6992727007011277</v>
+        <v>0.4844248901091631</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5752841088710083</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1239885918301193</v>
+        <v>0.2628639895549607</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5395,28 +6139,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>26.67068333333333</v>
+        <v>18.98408333333333</v>
       </c>
       <c r="D81" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>22.62068333333333</v>
+        <v>18.98408333333333</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4662856779261432</v>
+        <v>0.3753728936893338</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5525630686911562</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.08627739076501301</v>
+        <v>0.3753728936893338</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5425,28 +6169,28 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2.883333333333333</v>
+        <v>2.3</v>
       </c>
       <c r="D82" t="n">
-        <v>7.683333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="E82" t="n">
-        <v>-4.800000000000001</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2514853038814903</v>
+        <v>0.185676926950206</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6833899734934139</v>
+        <v>0.1164747371577703</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.4319046696119236</v>
+        <v>0.06920218979243568</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5455,28 +6199,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>61.42319999999999</v>
+        <v>58.60501666666666</v>
       </c>
       <c r="D83" t="n">
-        <v>38.68333333333333</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="E83" t="n">
-        <v>22.73986666666666</v>
+        <v>28.13834999999999</v>
       </c>
       <c r="F83" t="n">
-        <v>44.94924920648065</v>
+        <v>43.70509198694462</v>
       </c>
       <c r="G83" t="n">
-        <v>27.60990969505806</v>
+        <v>21.5665214603954</v>
       </c>
       <c r="H83" t="n">
-        <v>17.33933951142259</v>
+        <v>22.13857052654922</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5485,28 +6229,28 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>44.01666666666667</v>
+        <v>41.15</v>
       </c>
       <c r="D84" t="n">
-        <v>26.81666666666667</v>
+        <v>23</v>
       </c>
       <c r="E84" t="n">
-        <v>17.2</v>
+        <v>18.15</v>
       </c>
       <c r="F84" t="n">
-        <v>32.63164533881391</v>
+        <v>31.31100557837641</v>
       </c>
       <c r="G84" t="n">
-        <v>19.89292827190748</v>
+        <v>17.03068189911616</v>
       </c>
       <c r="H84" t="n">
-        <v>12.73871706690643</v>
+        <v>14.28032367926025</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PAIR_025</t>
+          <t>PAIR_022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5515,22 +6259,862 @@
         </is>
       </c>
       <c r="C85" t="n">
+        <v>69.61666666666666</v>
+      </c>
+      <c r="D85" t="n">
+        <v>134.3833333333333</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-64.76666666666664</v>
+      </c>
+      <c r="F85" t="n">
+        <v>65.77016461009407</v>
+      </c>
+      <c r="G85" t="n">
+        <v>102.738159054381</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-36.96799444428693</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>8.933333333333334</v>
+      </c>
+      <c r="D87" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-62.14999999999999</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.2591759316479205</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.5490512384335874</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.2898753067856669</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5.418866666666667</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.368866666666667</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.7086331393992357</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.1560700707080794</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>9.246550000000001</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-9.246550000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.8240664355600736</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0.8240664355600736</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>46.88333333333333</v>
+      </c>
+      <c r="D90" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="E90" t="n">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="F90" t="n">
+        <v>37.60330466808259</v>
+      </c>
+      <c r="G90" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="H90" t="n">
+        <v>9.993394973024532</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>35.66666666666666</v>
+      </c>
+      <c r="D91" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="E91" t="n">
+        <v>8.849999999999987</v>
+      </c>
+      <c r="F91" t="n">
+        <v>27.74280476419689</v>
+      </c>
+      <c r="G91" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="H91" t="n">
+        <v>7.849876492289411</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>116.9833333333333</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-18.48333333333331</v>
+      </c>
+      <c r="F92" t="n">
+        <v>79.5925237709541</v>
+      </c>
+      <c r="G92" t="n">
+        <v>96.56581198980894</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-16.97328821885483</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>12.03333333333333</v>
+      </c>
+      <c r="D94" t="n">
+        <v>48.18333333333333</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-36.15</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.3736603870816042</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.6526929809004927</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.2790325938188885</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>4.916666666666667</v>
+      </c>
+      <c r="D95" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-8.750000000000004</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.8124960099708274</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.252848098218356</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.4403520882475287</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.149895932972568</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-1.149895932972568</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>47.07095</v>
+      </c>
+      <c r="D97" t="n">
+        <v>47.50425</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-0.4332999999999956</v>
+      </c>
+      <c r="F97" t="n">
+        <v>37.76245819389838</v>
+      </c>
+      <c r="G97" t="n">
+        <v>30.80621122533811</v>
+      </c>
+      <c r="H97" t="n">
+        <v>6.956246968560272</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>35.88333333333333</v>
+      </c>
+      <c r="D98" t="n">
+        <v>34.78333333333333</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="F98" t="n">
+        <v>27.85743429121439</v>
+      </c>
+      <c r="G98" t="n">
+        <v>23.37216669639708</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4.485267594817309</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="D99" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="F99" t="n">
+        <v>81.8124074509457</v>
+      </c>
+      <c r="G99" t="n">
+        <v>91.31840822873183</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-9.506000777786127</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>45.16666666666666</v>
+      </c>
+      <c r="D101" t="n">
+        <v>71.08333333333333</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-25.91666666666667</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6992727007011277</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.5752841088710083</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.1239885918301193</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>26.67068333333333</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E102" t="n">
+        <v>22.62068333333333</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.4662856779261432</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.5525630686911562</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-0.08627739076501301</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2.883333333333333</v>
+      </c>
+      <c r="D103" t="n">
+        <v>7.683333333333334</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-4.800000000000001</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.2514853038814903</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.6833899734934139</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-0.4319046696119236</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>61.42319999999999</v>
+      </c>
+      <c r="D104" t="n">
+        <v>38.68333333333333</v>
+      </c>
+      <c r="E104" t="n">
+        <v>22.73986666666666</v>
+      </c>
+      <c r="F104" t="n">
+        <v>44.94924920648065</v>
+      </c>
+      <c r="G104" t="n">
+        <v>27.60990969505806</v>
+      </c>
+      <c r="H104" t="n">
+        <v>17.33933951142259</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>44.01666666666667</v>
+      </c>
+      <c r="D105" t="n">
+        <v>26.81666666666667</v>
+      </c>
+      <c r="E105" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F105" t="n">
+        <v>32.63164533881391</v>
+      </c>
+      <c r="G105" t="n">
+        <v>19.89292827190748</v>
+      </c>
+      <c r="H105" t="n">
+        <v>12.73871706690643</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
         <v>75.58333333333333</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D106" t="n">
         <v>117.3133166666667</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E106" t="n">
         <v>-41.72998333333337</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F106" t="n">
         <v>66.97939427620221</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G106" t="n">
         <v>96.5752612810128</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H106" t="n">
         <v>-29.59586700481059</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CHARGING / REFUELING</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>35.56666666666667</v>
+      </c>
+      <c r="D108" t="n">
+        <v>48.18333333333333</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-12.61666666666666</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.5933262321891101</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.6526929809004927</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-0.05936674871138259</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>30.98408333333333</v>
+      </c>
+      <c r="D109" t="n">
+        <v>17.66666666666667</v>
+      </c>
+      <c r="E109" t="n">
+        <v>13.31741666666666</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.608277485360332</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.46713538845297</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-0.8588579030926381</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>INCH</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>10.23333333333333</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-6.933333333333331</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.3072360563497603</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.325529204266642</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-1.018293147916882</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>67.48085</v>
+      </c>
+      <c r="D111" t="n">
+        <v>51.03333333333333</v>
+      </c>
+      <c r="E111" t="n">
+        <v>16.44751666666667</v>
+      </c>
+      <c r="F111" t="n">
+        <v>47.84822798746782</v>
+      </c>
+      <c r="G111" t="n">
+        <v>32.19479692464096</v>
+      </c>
+      <c r="H111" t="n">
+        <v>15.65343106282686</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>48.56666666666667</v>
+      </c>
+      <c r="D112" t="n">
+        <v>37.13333333333333</v>
+      </c>
+      <c r="E112" t="n">
+        <v>11.43333333333334</v>
+      </c>
+      <c r="F112" t="n">
+        <v>34.79805765976413</v>
+      </c>
+      <c r="G112" t="n">
+        <v>24.26414905968165</v>
+      </c>
+      <c r="H112" t="n">
+        <v>10.53390860008248</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CRUISE</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>79.91666666666667</v>
+      </c>
+      <c r="D113" t="n">
+        <v>121.3166666666667</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-41.40000000000003</v>
+      </c>
+      <c r="F113" t="n">
+        <v>69.52135128395038</v>
+      </c>
+      <c r="G113" t="n">
+        <v>93.62643672048709</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-24.10508543653671</v>
       </c>
     </row>
   </sheetData>
@@ -5616,22 +7200,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.06842361111111</v>
+        <v>28.72215104166666</v>
       </c>
       <c r="C3" t="n">
-        <v>57.45555555555556</v>
+        <v>55.1375</v>
       </c>
       <c r="D3" t="n">
-        <v>-31.38713194444444</v>
+        <v>-26.41534895833333</v>
       </c>
       <c r="E3" t="n">
-        <v>-36.60833333333333</v>
+        <v>-29.91666666666667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.416762105628732</v>
+        <v>0.4266363378704819</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5424605171682151</v>
+        <v>0.5700186331012845</v>
       </c>
     </row>
     <row r="4">
@@ -5641,22 +7225,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.44477777777778</v>
+        <v>13.08258854166667</v>
       </c>
       <c r="C4" t="n">
-        <v>4.666666666666667</v>
+        <v>7.666666666666668</v>
       </c>
       <c r="D4" t="n">
-        <v>7.778111111111111</v>
+        <v>5.415921874999999</v>
       </c>
       <c r="E4" t="n">
-        <v>5.060241666666668</v>
+        <v>4.855633333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9875851087199073</v>
+        <v>1.014442538100779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7835208996971215</v>
+        <v>0.9410315662464201</v>
       </c>
     </row>
     <row r="5">
@@ -5666,22 +7250,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.136111111111111</v>
+        <v>3.190625</v>
       </c>
       <c r="C5" t="n">
-        <v>4.378879166666667</v>
+        <v>5.695617708333334</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.242768055555556</v>
+        <v>-2.504992708333333</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4666666666666671</v>
+        <v>-1.691666666666666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2424896168078597</v>
+        <v>0.2530188041192101</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5171270905960592</v>
+        <v>0.7071730343972575</v>
       </c>
     </row>
     <row r="6">
@@ -5691,22 +7275,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51.95500000000001</v>
+        <v>52.9351125</v>
       </c>
       <c r="C6" t="n">
-        <v>31.42711944444444</v>
+        <v>36.10810520833333</v>
       </c>
       <c r="D6" t="n">
-        <v>20.52788055555556</v>
+        <v>16.82700729166667</v>
       </c>
       <c r="E6" t="n">
-        <v>21.82061666666667</v>
+        <v>16.40709166666667</v>
       </c>
       <c r="F6" t="n">
-        <v>41.02298235166946</v>
+        <v>41.49659041294439</v>
       </c>
       <c r="G6" t="n">
-        <v>21.73246776952415</v>
+        <v>24.26303735168147</v>
       </c>
     </row>
     <row r="7">
@@ -5716,22 +7300,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37.41874722222222</v>
+        <v>38.32194895833333</v>
       </c>
       <c r="C7" t="n">
-        <v>24.41666666666667</v>
+        <v>27.44895833333333</v>
       </c>
       <c r="D7" t="n">
-        <v>13.00208055555556</v>
+        <v>10.872990625</v>
       </c>
       <c r="E7" t="n">
-        <v>12.075</v>
+        <v>11.7</v>
       </c>
       <c r="F7" t="n">
-        <v>29.07212415296469</v>
+        <v>29.47326433356202</v>
       </c>
       <c r="G7" t="n">
-        <v>17.91146000917136</v>
+        <v>19.44388337409364</v>
       </c>
     </row>
     <row r="8">
@@ -5741,22 +7325,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88.59827777777777</v>
+        <v>91.182665625</v>
       </c>
       <c r="C8" t="n">
-        <v>131.9288875</v>
+        <v>128.8633322916666</v>
       </c>
       <c r="D8" t="n">
-        <v>-43.3306097222222</v>
+        <v>-37.68066666666665</v>
       </c>
       <c r="E8" t="n">
-        <v>-42.57144999999999</v>
+        <v>-41.873325</v>
       </c>
       <c r="F8" t="n">
-        <v>73.55007302317372</v>
+        <v>74.3931892697932</v>
       </c>
       <c r="G8" t="n">
-        <v>103.7803480898824</v>
+        <v>101.1018731623636</v>
       </c>
     </row>
   </sheetData>
@@ -5827,28 +7411,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>13.16666666666667</v>
+        <v>17.9375</v>
       </c>
       <c r="D2" t="n">
-        <v>7.51765598542202</v>
+        <v>12.54043460171935</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="G2" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="H2" t="n">
-        <v>18.25</v>
+        <v>23.5</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -5858,28 +7442,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>219.6213375</v>
+        <v>227.4350916666666</v>
       </c>
       <c r="D3" t="n">
-        <v>21.49761037932515</v>
+        <v>29.63802590171144</v>
       </c>
       <c r="E3" t="n">
         <v>186.11555</v>
       </c>
       <c r="F3" t="n">
-        <v>204.1775958333334</v>
+        <v>204.8461333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>220.5295083333333</v>
+        <v>221.3197583333333</v>
       </c>
       <c r="H3" t="n">
-        <v>234.7795833333333</v>
+        <v>242.1496375</v>
       </c>
       <c r="I3" t="n">
-        <v>255.7438833333333</v>
+        <v>299.5047</v>
       </c>
     </row>
     <row r="4">
@@ -5889,28 +7473,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>254.273775</v>
+        <v>260.9201802083333</v>
       </c>
       <c r="D4" t="n">
-        <v>24.62775367421587</v>
+        <v>24.57380075212611</v>
       </c>
       <c r="E4" t="n">
         <v>221.15</v>
       </c>
       <c r="F4" t="n">
-        <v>221.15</v>
+        <v>254.5099875</v>
       </c>
       <c r="G4" t="n">
-        <v>268.0399416666667</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>273.119075</v>
+        <v>274.35</v>
       </c>
       <c r="I4" t="n">
-        <v>274.35</v>
+        <v>285.5666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -5920,28 +7504,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>145.2920163589644</v>
+        <v>147.0571416963901</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8129708792688</v>
+        <v>4.124676198354017</v>
       </c>
       <c r="E5" t="n">
         <v>141.5990549680233</v>
       </c>
       <c r="F5" t="n">
-        <v>141.8032551508215</v>
+        <v>144.8877659272516</v>
       </c>
       <c r="G5" t="n">
-        <v>146.0438473668609</v>
+        <v>146.962080558246</v>
       </c>
       <c r="H5" t="n">
-        <v>147.904477923269</v>
+        <v>148.4606982942009</v>
       </c>
       <c r="I5" t="n">
-        <v>148.4081122812309</v>
+        <v>153.6764767050815</v>
       </c>
     </row>
     <row r="6">
@@ -5951,28 +7535,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>145.2673843760393</v>
+        <v>147.0270171218836</v>
       </c>
       <c r="D6" t="n">
-        <v>2.781898436675304</v>
+        <v>4.10316881579874</v>
       </c>
       <c r="E6" t="n">
         <v>141.6663057069586</v>
       </c>
       <c r="F6" t="n">
-        <v>141.7036465827298</v>
+        <v>144.845434655885</v>
       </c>
       <c r="G6" t="n">
-        <v>146.0942505451993</v>
+        <v>146.980627920884</v>
       </c>
       <c r="H6" t="n">
-        <v>147.8323860893165</v>
+        <v>148.2650623296203</v>
       </c>
       <c r="I6" t="n">
-        <v>148.1693420519742</v>
+        <v>153.5880362119665</v>
       </c>
     </row>
     <row r="7">
@@ -5982,25 +7566,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>47.78934717098331</v>
+        <v>47.24553057293302</v>
       </c>
       <c r="D7" t="n">
-        <v>2.194246102296493</v>
+        <v>2.530179228229419</v>
       </c>
       <c r="E7" t="n">
-        <v>42.80810564129094</v>
+        <v>41.13690324412203</v>
       </c>
       <c r="F7" t="n">
-        <v>47.25168896860315</v>
+        <v>46.91176584179654</v>
       </c>
       <c r="G7" t="n">
-        <v>48.0710590752668</v>
+        <v>47.70402310254107</v>
       </c>
       <c r="H7" t="n">
-        <v>49.05246220138098</v>
+        <v>48.97810035627302</v>
       </c>
       <c r="I7" t="n">
         <v>51.08928882117495</v>
@@ -6013,25 +7597,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>44.94682319696793</v>
+        <v>44.14809039114164</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2586388852712208</v>
+        <v>1.488964501155783</v>
       </c>
       <c r="E8" t="n">
-        <v>44.7845362014835</v>
+        <v>41.34713516442955</v>
       </c>
       <c r="F8" t="n">
-        <v>44.81458420079127</v>
+        <v>44.32453459732769</v>
       </c>
       <c r="G8" t="n">
-        <v>44.82873076476382</v>
+        <v>44.82085375106323</v>
       </c>
       <c r="H8" t="n">
-        <v>44.90411641857893</v>
+        <v>44.85118124932704</v>
       </c>
       <c r="I8" t="n">
         <v>45.59497163487288</v>
@@ -6044,19 +7628,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-34.65243750000002</v>
+        <v>-33.4850885416667</v>
       </c>
       <c r="D9" t="n">
-        <v>23.62088669813258</v>
+        <v>25.56973997120767</v>
       </c>
       <c r="E9" t="n">
         <v>-72.92863333333338</v>
       </c>
       <c r="F9" t="n">
-        <v>-50.16829166666665</v>
+        <v>-50.58460416666671</v>
       </c>
       <c r="G9" t="n">
         <v>-34.47040833333335</v>
@@ -6065,7 +7649,7 @@
         <v>-14.51945833333331</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02756666666670071</v>
+        <v>13.93803333333329</v>
       </c>
     </row>
     <row r="10">
@@ -6075,19 +7659,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0246319829250865</v>
+        <v>0.03012457450645378</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1087019112084609</v>
+        <v>0.09957961304083307</v>
       </c>
       <c r="E10" t="n">
         <v>-0.1087673906557995</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.07139009450725808</v>
+        <v>-0.05363884912173944</v>
       </c>
       <c r="G10" t="n">
         <v>0.03113644488620082</v>
@@ -6106,13 +7690,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>2.842523974015379</v>
+        <v>3.097440181791379</v>
       </c>
       <c r="D11" t="n">
-        <v>2.21385178372173</v>
+        <v>2.326181758132269</v>
       </c>
       <c r="E11" t="n">
         <v>-1.976430560192554</v>
@@ -6121,13 +7705,13 @@
         <v>2.236735495546228</v>
       </c>
       <c r="G11" t="n">
-        <v>2.952793577434512</v>
+        <v>3.592883364884511</v>
       </c>
       <c r="H11" t="n">
-        <v>4.220536450493544</v>
+        <v>4.526895626622483</v>
       </c>
       <c r="I11" t="n">
-        <v>6.26919540483344</v>
+        <v>6.35936854540796</v>
       </c>
     </row>
     <row r="12">
@@ -6137,25 +7721,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-23.60902083333334</v>
+        <v>-20.99942708333333</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25470265736834</v>
+        <v>25.49233465724614</v>
       </c>
       <c r="E12" t="n">
         <v>-62.65000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-38.718825</v>
+        <v>-38.593825</v>
       </c>
       <c r="G12" t="n">
-        <v>-24.56774166666666</v>
+        <v>-18.91103333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.717820833333339</v>
+        <v>-0.5623125000000035</v>
       </c>
       <c r="I12" t="n">
         <v>17.65075</v>
@@ -6168,7 +7752,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -6199,7 +7783,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -6230,7 +7814,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -6261,7 +7845,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -6292,7 +7876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -6323,7 +7907,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -6354,13 +7938,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>26.06842361111111</v>
+        <v>28.72215104166666</v>
       </c>
       <c r="D19" t="n">
-        <v>10.95654748309503</v>
+        <v>14.94610631055791</v>
       </c>
       <c r="E19" t="n">
         <v>8.933333333333334</v>
@@ -6369,13 +7953,13 @@
         <v>22.42083333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>29.793875</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>30.25416666666666</v>
+        <v>31.74166666666667</v>
       </c>
       <c r="I19" t="n">
-        <v>45.16666666666666</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="20">
@@ -6385,25 +7969,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>57.45555555555556</v>
+        <v>55.1375</v>
       </c>
       <c r="D20" t="n">
-        <v>18.96016202746548</v>
+        <v>16.75765994005925</v>
       </c>
       <c r="E20" t="n">
         <v>31.8</v>
       </c>
       <c r="F20" t="n">
-        <v>31.8</v>
+        <v>44.0875</v>
       </c>
       <c r="G20" t="n">
-        <v>69.48333333333333</v>
+        <v>58.83333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>71.08333333333333</v>
+        <v>69.88333333333333</v>
       </c>
       <c r="I20" t="n">
         <v>71.08333333333333</v>
@@ -6416,28 +8000,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-31.38713194444444</v>
+        <v>-26.41534895833333</v>
       </c>
       <c r="D21" t="n">
-        <v>20.40719378685777</v>
+        <v>22.30058357076108</v>
       </c>
       <c r="E21" t="n">
         <v>-62.14999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-42.15918749999999</v>
+        <v>-41.09472916666667</v>
       </c>
       <c r="G21" t="n">
-        <v>-36.60833333333333</v>
+        <v>-29.91666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>-18.62916666666667</v>
+        <v>-10.94166666666666</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.333333333333332</v>
+        <v>20.76666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -6447,25 +8031,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4167621056287321</v>
+        <v>0.426636337870482</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1282600464522988</v>
+        <v>0.1202649493747244</v>
       </c>
       <c r="E22" t="n">
         <v>0.2591759316479205</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3556868609874803</v>
+        <v>0.3691670055580732</v>
       </c>
       <c r="G22" t="n">
         <v>0.3830658150971378</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4747597427034639</v>
+        <v>0.4773440005385971</v>
       </c>
       <c r="I22" t="n">
         <v>0.6992727007011277</v>
@@ -6478,25 +8062,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>0.542460517168215</v>
+        <v>0.5700186331012844</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2642918694221398</v>
+        <v>0.2316327125502221</v>
       </c>
       <c r="E23" t="n">
         <v>0.2215609005542024</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2215609005542024</v>
+        <v>0.4671786539637411</v>
       </c>
       <c r="G23" t="n">
-        <v>0.569717341030624</v>
+        <v>0.6139885448857505</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8398781436089819</v>
+        <v>0.699489271577615</v>
       </c>
       <c r="I23" t="n">
         <v>0.8398781436089819</v>
@@ -6509,25 +8093,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1256984115394831</v>
+        <v>-0.1433822952308025</v>
       </c>
       <c r="D24" t="n">
-        <v>0.268080513568443</v>
+        <v>0.2362014875474764</v>
       </c>
       <c r="E24" t="n">
         <v>-0.4841912826215016</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3316095622172112</v>
+        <v>-0.281743272060583</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1424154200312731</v>
+        <v>-0.183308793696169</v>
       </c>
       <c r="H24" t="n">
-        <v>0.126522933980909</v>
+        <v>0.05920842127781842</v>
       </c>
       <c r="I24" t="n">
         <v>0.2628639895549607</v>
@@ -6540,13 +8124,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>12.44477777777778</v>
+        <v>13.08258854166667</v>
       </c>
       <c r="D25" t="n">
-        <v>7.929244283147984</v>
+        <v>8.625878375368867</v>
       </c>
       <c r="E25" t="n">
         <v>4.75</v>
@@ -6558,10 +8142,10 @@
         <v>10.645975</v>
       </c>
       <c r="H25" t="n">
-        <v>15.46465833333334</v>
+        <v>16.69602083333333</v>
       </c>
       <c r="I25" t="n">
-        <v>26.67068333333333</v>
+        <v>30.98408333333333</v>
       </c>
     </row>
     <row r="26">
@@ -6571,28 +8155,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>4.666666666666666</v>
+        <v>7.666666666666668</v>
       </c>
       <c r="D26" t="n">
-        <v>4.267069109808134</v>
+        <v>6.553811444071646</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3.0375</v>
       </c>
       <c r="G26" t="n">
-        <v>4.05</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>9.949999999999999</v>
+        <v>10.87916666666667</v>
       </c>
       <c r="I26" t="n">
-        <v>9.949999999999999</v>
+        <v>17.66666666666667</v>
       </c>
     </row>
     <row r="27">
@@ -6602,25 +8186,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>7.778111111111111</v>
+        <v>5.415921874999998</v>
       </c>
       <c r="D27" t="n">
-        <v>8.40201438706343</v>
+        <v>9.594069599882888</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.199999999999999</v>
+        <v>-9.516666666666671</v>
       </c>
       <c r="F27" t="n">
-        <v>3.59835416666667</v>
+        <v>-1.750000000000006</v>
       </c>
       <c r="G27" t="n">
-        <v>5.060241666666668</v>
+        <v>4.855633333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>13.09502916666667</v>
+        <v>12.37045416666666</v>
       </c>
       <c r="I27" t="n">
         <v>22.62068333333333</v>
@@ -6633,28 +8217,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9875851087199073</v>
+        <v>1.014442538100779</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7428811852973265</v>
+        <v>0.7461684883506141</v>
       </c>
       <c r="E28" t="n">
         <v>0.3753728936893338</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4973888049654114</v>
+        <v>0.5585705132466763</v>
       </c>
       <c r="G28" t="n">
         <v>0.7050773259806996</v>
       </c>
       <c r="H28" t="n">
-        <v>1.062088812265765</v>
+        <v>1.128953816032191</v>
       </c>
       <c r="I28" t="n">
-        <v>2.33611605697715</v>
+        <v>2.383435777694972</v>
       </c>
     </row>
     <row r="29">
@@ -6664,25 +8248,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7835208996971215</v>
+        <v>0.9410315662464203</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7854156085709972</v>
+        <v>0.730796598505591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.4144223015183672</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5525630686911562</v>
+        <v>0.9027055834547562</v>
       </c>
       <c r="H29" t="n">
-        <v>1.797999630400208</v>
+        <v>1.549851448939779</v>
       </c>
       <c r="I29" t="n">
         <v>1.797999630400208</v>
@@ -6695,22 +8279,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2040642090227859</v>
+        <v>0.07341097185435885</v>
       </c>
       <c r="D30" t="n">
-        <v>1.048514002736508</v>
+        <v>1.002404452201015</v>
       </c>
       <c r="E30" t="n">
         <v>-1.29126767325584</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3388275725332709</v>
+        <v>-0.8669647664458597</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2730762483068848</v>
+        <v>0.1634248368162576</v>
       </c>
       <c r="H30" t="n">
         <v>0.5835144426087651</v>
@@ -6726,13 +8310,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>3.136111111111111</v>
+        <v>3.190625</v>
       </c>
       <c r="D31" t="n">
-        <v>2.864567883337583</v>
+        <v>2.88641754602483</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -6757,13 +8341,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>4.378879166666667</v>
+        <v>5.695617708333334</v>
       </c>
       <c r="D32" t="n">
-        <v>4.295902727823979</v>
+        <v>4.381021263212616</v>
       </c>
       <c r="E32" t="n">
         <v>1.266666666666667</v>
@@ -6772,10 +8356,10 @@
         <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1.716666666666667</v>
+        <v>4.7</v>
       </c>
       <c r="H32" t="n">
-        <v>8.074137500000001</v>
+        <v>9.9</v>
       </c>
       <c r="I32" t="n">
         <v>11.6</v>
@@ -6788,25 +8372,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.242768055555556</v>
+        <v>-2.504992708333333</v>
       </c>
       <c r="D33" t="n">
-        <v>4.488065159383455</v>
+        <v>4.656639897015908</v>
       </c>
       <c r="E33" t="n">
         <v>-9.246550000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.887499999999999</v>
+        <v>-7.041666666666664</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4666666666666671</v>
+        <v>-1.691666666666666</v>
       </c>
       <c r="H33" t="n">
-        <v>0.65</v>
+        <v>0.4374999999999998</v>
       </c>
       <c r="I33" t="n">
         <v>6.300000000000001</v>
@@ -6819,13 +8403,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2424896168078597</v>
+        <v>0.2530188041192101</v>
       </c>
       <c r="D34" t="n">
-        <v>0.212245330049233</v>
+        <v>0.2169031514009851</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -6837,7 +8421,7 @@
         <v>0.2046142102738726</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2945670087065282</v>
+        <v>0.3195534807121517</v>
       </c>
       <c r="I34" t="n">
         <v>0.6265751975894123</v>
@@ -6850,28 +8434,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5171270905960593</v>
+        <v>0.7071730343972575</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3413832744129097</v>
+        <v>0.4499853094152342</v>
       </c>
       <c r="E35" t="n">
         <v>0.1164747371577703</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1164747371577703</v>
+        <v>0.3783103562951116</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5759078527107181</v>
+        <v>0.6296489131020659</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7185590890100788</v>
+        <v>1.062494332977064</v>
       </c>
       <c r="I35" t="n">
-        <v>1.033360466311896</v>
+        <v>1.325529204266642</v>
       </c>
     </row>
     <row r="36">
@@ -6881,25 +8465,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2746374737881995</v>
+        <v>-0.4541542302780475</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3409348678945429</v>
+        <v>0.4439637319270809</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8240664355600736</v>
+        <v>-1.149895932972568</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4403257262108324</v>
+        <v>-0.7755963883672436</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3751076269319831</v>
+        <v>-0.4139523406640898</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05530105610712956</v>
+        <v>-0.07468921664865419</v>
       </c>
       <c r="I36" t="n">
         <v>0.2400310166415557</v>
@@ -6912,28 +8496,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>51.95499999999999</v>
+        <v>52.9351125</v>
       </c>
       <c r="D37" t="n">
-        <v>6.693003396669408</v>
+        <v>7.230755255935629</v>
       </c>
       <c r="E37" t="n">
         <v>43.83333333333334</v>
       </c>
       <c r="F37" t="n">
-        <v>46.75</v>
+        <v>46.89583333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>50.21278333333333</v>
+        <v>51.49166666666667</v>
       </c>
       <c r="H37" t="n">
-        <v>56.56375416666666</v>
+        <v>58.37625416666666</v>
       </c>
       <c r="I37" t="n">
-        <v>63.03526666666667</v>
+        <v>67.48085</v>
       </c>
     </row>
     <row r="38">
@@ -6943,28 +8527,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>31.42711944444445</v>
+        <v>36.10810520833333</v>
       </c>
       <c r="D38" t="n">
-        <v>5.821956222617308</v>
+        <v>9.777340706490921</v>
       </c>
       <c r="E38" t="n">
         <v>25.12543333333333</v>
       </c>
       <c r="F38" t="n">
-        <v>25.13333333333333</v>
+        <v>29.13333333333333</v>
       </c>
       <c r="G38" t="n">
-        <v>30.46666666666667</v>
+        <v>34.575</v>
       </c>
       <c r="H38" t="n">
-        <v>38.68333333333333</v>
+        <v>40.8885625</v>
       </c>
       <c r="I38" t="n">
-        <v>38.68333333333333</v>
+        <v>51.03333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -6974,25 +8558,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>20.52788055555556</v>
+        <v>16.82700729166667</v>
       </c>
       <c r="D39" t="n">
-        <v>9.042792935223886</v>
+        <v>10.79971869380208</v>
       </c>
       <c r="E39" t="n">
-        <v>7.666666666666671</v>
+        <v>-0.4332999999999956</v>
       </c>
       <c r="F39" t="n">
-        <v>14.29487916666667</v>
+        <v>8.06666666666667</v>
       </c>
       <c r="G39" t="n">
-        <v>21.82061666666667</v>
+        <v>16.40709166666667</v>
       </c>
       <c r="H39" t="n">
-        <v>24.2537625</v>
+        <v>22.79462499999999</v>
       </c>
       <c r="I39" t="n">
         <v>37.90193333333335</v>
@@ -7005,28 +8589,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>41.02298235166948</v>
+        <v>41.49659041294439</v>
       </c>
       <c r="D40" t="n">
-        <v>3.690357573661512</v>
+        <v>3.88618219083838</v>
       </c>
       <c r="E40" t="n">
         <v>36.70010973267537</v>
       </c>
       <c r="F40" t="n">
-        <v>37.606340707808</v>
+        <v>37.72368182568624</v>
       </c>
       <c r="G40" t="n">
-        <v>40.94369908853516</v>
+        <v>41.76873769232874</v>
       </c>
       <c r="H40" t="n">
-        <v>44.47366833289454</v>
+        <v>44.82035823385822</v>
       </c>
       <c r="I40" t="n">
-        <v>45.7896379485424</v>
+        <v>47.84822798746782</v>
       </c>
     </row>
     <row r="41">
@@ -7036,28 +8620,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>21.73246776952415</v>
+        <v>24.26303735168147</v>
       </c>
       <c r="D41" t="n">
-        <v>4.933546834869</v>
+        <v>6.199929794102298</v>
       </c>
       <c r="E41" t="n">
         <v>16.04368253659841</v>
       </c>
       <c r="F41" t="n">
-        <v>16.04586173141521</v>
+        <v>20.15184117641193</v>
       </c>
       <c r="G41" t="n">
-        <v>21.54277919776302</v>
+        <v>24.58821557772673</v>
       </c>
       <c r="H41" t="n">
-        <v>27.60990969505806</v>
+        <v>28.40898507762807</v>
       </c>
       <c r="I41" t="n">
-        <v>27.60990969505806</v>
+        <v>32.22664079654989</v>
       </c>
     </row>
     <row r="42">
@@ -7067,25 +8651,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>19.29051458214531</v>
+        <v>17.23355306126292</v>
       </c>
       <c r="D42" t="n">
-        <v>6.298571972161881</v>
+        <v>6.796007110260983</v>
       </c>
       <c r="E42" t="n">
-        <v>9.993394973024532</v>
+        <v>6.956246968560272</v>
       </c>
       <c r="F42" t="n">
-        <v>15.25036834870169</v>
+        <v>12.80247766769301</v>
       </c>
       <c r="G42" t="n">
-        <v>19.45005205139246</v>
+        <v>16.20797380976119</v>
       </c>
       <c r="H42" t="n">
-        <v>22.25202481469283</v>
+        <v>21.83142346446619</v>
       </c>
       <c r="I42" t="n">
         <v>29.74595541194399</v>
@@ -7098,28 +8682,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>37.41874722222222</v>
+        <v>38.32194895833334</v>
       </c>
       <c r="D43" t="n">
-        <v>4.676515648557558</v>
+        <v>5.041801289557905</v>
       </c>
       <c r="E43" t="n">
         <v>30.25</v>
       </c>
       <c r="F43" t="n">
-        <v>34.58750000000001</v>
+        <v>35.40416666666667</v>
       </c>
       <c r="G43" t="n">
-        <v>36.62081666666666</v>
+        <v>37.31725833333333</v>
       </c>
       <c r="H43" t="n">
-        <v>40.375</v>
+        <v>41.51666666666667</v>
       </c>
       <c r="I43" t="n">
-        <v>45.45</v>
+        <v>48.56666666666667</v>
       </c>
     </row>
     <row r="44">
@@ -7129,28 +8713,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>24.41666666666667</v>
+        <v>27.44895833333333</v>
       </c>
       <c r="D44" t="n">
-        <v>1.782122216897484</v>
+        <v>5.659372654507971</v>
       </c>
       <c r="E44" t="n">
         <v>23</v>
       </c>
       <c r="F44" t="n">
-        <v>23</v>
+        <v>23.325</v>
       </c>
       <c r="G44" t="n">
-        <v>23.43333333333333</v>
+        <v>25.125</v>
       </c>
       <c r="H44" t="n">
-        <v>26.81666666666667</v>
+        <v>28.80833333333334</v>
       </c>
       <c r="I44" t="n">
-        <v>26.81666666666667</v>
+        <v>37.13333333333333</v>
       </c>
     </row>
     <row r="45">
@@ -7160,25 +8744,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>13.00208055555556</v>
+        <v>10.872990625</v>
       </c>
       <c r="D45" t="n">
-        <v>4.906758596500855</v>
+        <v>6.131562943111015</v>
       </c>
       <c r="E45" t="n">
-        <v>5.166666666666661</v>
+        <v>-0.07378333333334552</v>
       </c>
       <c r="F45" t="n">
-        <v>9.725000000000001</v>
+        <v>6.808333333333334</v>
       </c>
       <c r="G45" t="n">
-        <v>12.075</v>
+        <v>11.7</v>
       </c>
       <c r="H45" t="n">
-        <v>16.8125</v>
+        <v>15.10205833333334</v>
       </c>
       <c r="I45" t="n">
         <v>22.01666666666667</v>
@@ -7191,28 +8775,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>29.07212415296469</v>
+        <v>29.47326433356202</v>
       </c>
       <c r="D46" t="n">
-        <v>2.820642436973817</v>
+        <v>2.944404478642465</v>
       </c>
       <c r="E46" t="n">
         <v>24.89543913557874</v>
       </c>
       <c r="F46" t="n">
-        <v>27.04170208891873</v>
+        <v>27.53133765699798</v>
       </c>
       <c r="G46" t="n">
-        <v>29.01242314446199</v>
+        <v>29.09193512985015</v>
       </c>
       <c r="H46" t="n">
-        <v>31.10082900058318</v>
+        <v>31.52060888764839</v>
       </c>
       <c r="I46" t="n">
-        <v>33.36307095293761</v>
+        <v>34.79805765976413</v>
       </c>
     </row>
     <row r="47">
@@ -7222,28 +8806,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>17.91146000917135</v>
+        <v>19.44388337409364</v>
       </c>
       <c r="D47" t="n">
-        <v>1.468392570201946</v>
+        <v>3.02251654833124</v>
       </c>
       <c r="E47" t="n">
         <v>16.77959665852362</v>
       </c>
       <c r="F47" t="n">
-        <v>16.77959665852362</v>
+        <v>16.96791058896802</v>
       </c>
       <c r="G47" t="n">
-        <v>17.07123764974337</v>
+        <v>18.48359573081823</v>
       </c>
       <c r="H47" t="n">
-        <v>19.89292827190748</v>
+        <v>20.76273787802988</v>
       </c>
       <c r="I47" t="n">
-        <v>19.89292827190748</v>
+        <v>24.26414905968165</v>
       </c>
     </row>
     <row r="48">
@@ -7253,25 +8837,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>11.16066414379333</v>
+        <v>10.02938095946837</v>
       </c>
       <c r="D48" t="n">
-        <v>3.158477689494613</v>
+        <v>3.665480536784491</v>
       </c>
       <c r="E48" t="n">
-        <v>5.830029835698312</v>
+        <v>3.637679675291562</v>
       </c>
       <c r="F48" t="n">
-        <v>9.092783881227627</v>
+        <v>7.843804114058681</v>
       </c>
       <c r="G48" t="n">
-        <v>10.8165856206056</v>
+        <v>10.37651026400079</v>
       </c>
       <c r="H48" t="n">
-        <v>13.46985715678824</v>
+        <v>12.85639239554297</v>
       </c>
       <c r="I48" t="n">
         <v>16.58347429441399</v>
@@ -7284,28 +8868,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>88.59827777777777</v>
+        <v>91.182665625</v>
       </c>
       <c r="D49" t="n">
-        <v>10.67225357170662</v>
+        <v>12.00080674903809</v>
       </c>
       <c r="E49" t="n">
         <v>69.61666666666666</v>
       </c>
       <c r="F49" t="n">
-        <v>81.09604583333333</v>
+        <v>82.17937916666666</v>
       </c>
       <c r="G49" t="n">
-        <v>92.34999999999999</v>
+        <v>92.82499999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>94.67500000000001</v>
+        <v>99.9906625</v>
       </c>
       <c r="I49" t="n">
-        <v>102.3936333333333</v>
+        <v>113.4713666666667</v>
       </c>
     </row>
     <row r="50">
@@ -7315,25 +8899,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>131.9288874999999</v>
+        <v>128.8633322916666</v>
       </c>
       <c r="D50" t="n">
-        <v>11.77349010299878</v>
+        <v>11.59881777660257</v>
       </c>
       <c r="E50" t="n">
-        <v>116.9833333333333</v>
+        <v>114.05</v>
       </c>
       <c r="F50" t="n">
         <v>117.2308208333334</v>
       </c>
       <c r="G50" t="n">
-        <v>134.3833333333333</v>
+        <v>128.0166666666667</v>
       </c>
       <c r="H50" t="n">
-        <v>143.7458333333333</v>
+        <v>136.65</v>
       </c>
       <c r="I50" t="n">
         <v>144.6333333333333</v>
@@ -7346,28 +8930,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-43.3306097222222</v>
+        <v>-37.68066666666665</v>
       </c>
       <c r="D51" t="n">
-        <v>15.52639965022991</v>
+        <v>17.9911649728724</v>
       </c>
       <c r="E51" t="n">
         <v>-69.6333333333333</v>
       </c>
       <c r="F51" t="n">
-        <v>-51.28742916666663</v>
+        <v>-48.17937083333329</v>
       </c>
       <c r="G51" t="n">
-        <v>-42.57144999999999</v>
+        <v>-41.873325</v>
       </c>
       <c r="H51" t="n">
-        <v>-37.45998750000002</v>
+        <v>-23.23617916666665</v>
       </c>
       <c r="I51" t="n">
-        <v>-18.48333333333331</v>
+        <v>-8.178633333333309</v>
       </c>
     </row>
     <row r="52">
@@ -7377,28 +8961,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>73.55007302317372</v>
+        <v>74.3931892697932</v>
       </c>
       <c r="D52" t="n">
-        <v>6.106445159595658</v>
+        <v>6.121785612953421</v>
       </c>
       <c r="E52" t="n">
         <v>65.77016461009407</v>
       </c>
       <c r="F52" t="n">
-        <v>67.72642658111778</v>
+        <v>68.90994114760201</v>
       </c>
       <c r="G52" t="n">
-        <v>73.78896644386801</v>
+        <v>75.34031614614858</v>
       </c>
       <c r="H52" t="n">
-        <v>79.50266411531703</v>
+        <v>79.78485848934736</v>
       </c>
       <c r="I52" t="n">
-        <v>81.51318776562465</v>
+        <v>82.42120168353226</v>
       </c>
     </row>
     <row r="53">
@@ -7408,25 +8992,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>103.7803480898824</v>
+        <v>101.1018731623636</v>
       </c>
       <c r="D53" t="n">
-        <v>6.640206831295481</v>
+        <v>7.45409829219167</v>
       </c>
       <c r="E53" t="n">
-        <v>96.56581198980894</v>
+        <v>91.31840822873183</v>
       </c>
       <c r="F53" t="n">
-        <v>96.57289895821184</v>
+        <v>95.83948619820654</v>
       </c>
       <c r="G53" t="n">
-        <v>102.738159054381</v>
+        <v>99.6567101676969</v>
       </c>
       <c r="H53" t="n">
-        <v>111.875881290185</v>
+        <v>105.0048834823254</v>
       </c>
       <c r="I53" t="n">
         <v>112.1322772301322</v>
@@ -7439,28 +9023,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-30.23027506670869</v>
+        <v>-26.70868389257036</v>
       </c>
       <c r="D54" t="n">
-        <v>8.48478324998926</v>
+        <v>10.10447851549108</v>
       </c>
       <c r="E54" t="n">
         <v>-44.15683988070923</v>
       </c>
       <c r="F54" t="n">
-        <v>-36.1153066385055</v>
+        <v>-32.77123842313517</v>
       </c>
       <c r="G54" t="n">
-        <v>-29.94386800267227</v>
+        <v>-26.66854397920462</v>
       </c>
       <c r="H54" t="n">
-        <v>-25.87179405563644</v>
+        <v>-19.06721136808311</v>
       </c>
       <c r="I54" t="n">
-        <v>-16.97328821885483</v>
+        <v>-9.506000777786127</v>
       </c>
     </row>
   </sheetData>
@@ -7516,16 +9100,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>219.6213375</v>
+        <v>227.4350916666666</v>
       </c>
       <c r="D2" t="n">
-        <v>254.273775</v>
+        <v>260.9201802083334</v>
       </c>
       <c r="E2" t="n">
-        <v>-34.65243750000001</v>
+        <v>-33.4850885416667</v>
       </c>
       <c r="F2" t="n">
         <v>-34.47040833333335</v>
